--- a/outputs/EMS upgrade output - dearator.xlsx
+++ b/outputs/EMS upgrade output - dearator.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J16"/>
+  <dimension ref="A1:J106"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -471,12 +471,12 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t xml:space="preserve">VEDA </t>
+          <t xml:space="preserve">VEDA - Dearator </t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Remove dissolved oxygen from seawater/process water by contacting with stripping gas or vacuum to meet process water quality specifications for corrosion control in injection systems </t>
+          <t xml:space="preserve">Remove dissolved oxygen from process water to prevent downstream corrosion </t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
@@ -486,12 +486,12 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Contain deaerated water and maintain pressure boundary integrity under operating conditions </t>
+          <t xml:space="preserve">Contain process water under vacuum or stripping gas pressure </t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t xml:space="preserve">PDE – Parameter deviation </t>
+          <t xml:space="preserve">ELP - External leakage - process medium </t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
@@ -501,12 +501,12 @@
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t xml:space="preserve">General wall thinning reduces pressure containment capacity below design limits </t>
+          <t xml:space="preserve">Corrosion perforation of shell causes water leak to environment </t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Ultrasonic thickness measurement at critical locations [Y/N]; Visual inspection for corrosion damage [Y/N] </t>
+          <t xml:space="preserve">Shell wall ultrasonic thickness measured? [Y/N] </t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
@@ -516,19 +516,19 @@
       </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Predictive; Preventive </t>
+          <t xml:space="preserve">Predictive </t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t xml:space="preserve">VEDA </t>
+          <t xml:space="preserve">VEDA - Dearator </t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t xml:space="preserve">Remove dissolved oxygen from seawater/process water by contacting with stripping gas or vacuum to meet process water quality specifications for corrosion control in injection systems </t>
+          <t xml:space="preserve">Remove dissolved oxygen from process water to prevent downstream corrosion </t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
@@ -538,27 +538,27 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t xml:space="preserve">Contain deaerated water and maintain pressure boundary integrity under operating conditions </t>
+          <t xml:space="preserve">Contain process water under vacuum or stripping gas pressure </t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t xml:space="preserve">PDE – Parameter deviation </t>
+          <t xml:space="preserve">ELP - External leakage - process medium </t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t xml:space="preserve">2.4 Wear </t>
+          <t xml:space="preserve">2.6 Fatigue </t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t xml:space="preserve">Localized erosion at high velocity zones reduces wall thickness </t>
+          <t xml:space="preserve">Cyclic vacuum/pressure fluctuation causes through-wall crack </t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t xml:space="preserve">Internal visual inspection for erosion damage [Y/N]; Impingement plate condition check [Y/N] </t>
+          <t xml:space="preserve">Visual inspection of shell for cracks performed? [Y/N] </t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
@@ -568,19 +568,19 @@
       </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t xml:space="preserve">Predictive; Preventive </t>
+          <t xml:space="preserve">Preventive </t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t xml:space="preserve">VEDA </t>
+          <t xml:space="preserve">VEDA - Dearator </t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t xml:space="preserve">Remove dissolved oxygen from seawater/process water by contacting with stripping gas or vacuum to meet process water quality specifications for corrosion control in injection systems </t>
+          <t xml:space="preserve">Remove dissolved oxygen from process water to prevent downstream corrosion </t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
@@ -590,27 +590,27 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t xml:space="preserve">Contain deaerated water and maintain pressure boundary integrity under operating conditions </t>
+          <t xml:space="preserve">Contain process water under vacuum or stripping gas pressure </t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t xml:space="preserve">PDE – Parameter deviation </t>
+          <t xml:space="preserve">ELP - External leakage - process medium </t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t xml:space="preserve">1.4 Deformation </t>
+          <t xml:space="preserve">2.3 Erosion </t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t xml:space="preserve">Thermal distortion causes dimensional changes affecting internal clearances </t>
+          <t xml:space="preserve">High-velocity water impingement erodes internal wall </t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t xml:space="preserve">External visual inspection for bulging/dents [Y/N]; Temperature monitoring [Y/N] </t>
+          <t xml:space="preserve">Internal shell condition inspected via manhole? [Y/N] </t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
@@ -620,19 +620,19 @@
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t xml:space="preserve">Preventive; Predictive </t>
+          <t xml:space="preserve">Preventive </t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t xml:space="preserve">VEDA </t>
+          <t xml:space="preserve">VEDA - Dearator </t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t xml:space="preserve">Remove dissolved oxygen from seawater/process water by contacting with stripping gas or vacuum to meet process water quality specifications for corrosion control in injection systems </t>
+          <t xml:space="preserve">Remove dissolved oxygen from process water to prevent downstream corrosion </t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -642,27 +642,27 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t xml:space="preserve">Contain deaerated water and maintain pressure boundary integrity under operating conditions </t>
+          <t xml:space="preserve">Contain process water under vacuum or stripping gas pressure </t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t xml:space="preserve">STD – Structural deficiency </t>
+          <t xml:space="preserve">ELP - External leakage - process medium </t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t xml:space="preserve">2.6 Fatigue </t>
+          <t xml:space="preserve">1.4 Deformation </t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t xml:space="preserve">Cyclic pressure and thermal stress causes crack initiation in shell material or weld joints </t>
+          <t xml:space="preserve">Localized bulging due to vacuum collapse or mechanical damage </t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t xml:space="preserve">Weld NDT inspection (MPI/DP) during turnarounds [Y/N]; Pressure test verification [Y/N] </t>
+          <t xml:space="preserve">Shell exterior free from visible deformation? [Y/N] </t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
@@ -672,19 +672,19 @@
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t xml:space="preserve">Predictive; Failure-Finding </t>
+          <t xml:space="preserve">Preventive </t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t xml:space="preserve">VEDA </t>
+          <t xml:space="preserve">VEDA - Dearator </t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t xml:space="preserve">Remove dissolved oxygen from seawater/process water by contacting with stripping gas or vacuum to meet process water quality specifications for corrosion control in injection systems </t>
+          <t xml:space="preserve">Remove dissolved oxygen from process water to prevent downstream corrosion </t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
@@ -694,27 +694,27 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t xml:space="preserve">Contain deaerated water and maintain pressure boundary integrity under operating conditions </t>
+          <t xml:space="preserve">Contain process water under vacuum or stripping gas pressure </t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t xml:space="preserve">STD – Structural deficiency </t>
+          <t xml:space="preserve">STD - Structural deficiency </t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t xml:space="preserve">2.5 Breakage </t>
+          <t xml:space="preserve">2.2 Corrosion </t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t xml:space="preserve">Overpressure event or mechanical impact causes rupture or permanent structural damage </t>
+          <t xml:space="preserve">Generalized corrosion reduces load-bearing capacity </t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t xml:space="preserve">Overpressure protection device function test [Y/N]; Visual inspection for impact damage [Y/N] </t>
+          <t xml:space="preserve">Minimum wall thickness verified against corrosion allowance? [Y/N] </t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
@@ -724,19 +724,19 @@
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t xml:space="preserve">Preventive; Preventive </t>
+          <t xml:space="preserve">Predictive </t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t xml:space="preserve">VEDA </t>
+          <t xml:space="preserve">VEDA - Dearator </t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t xml:space="preserve">Remove dissolved oxygen from seawater/process water by contacting with stripping gas or vacuum to meet process water quality specifications for corrosion control in injection systems </t>
+          <t xml:space="preserve">Remove dissolved oxygen from process water to prevent downstream corrosion </t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
@@ -746,27 +746,27 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t xml:space="preserve">Contain deaerated water and maintain pressure boundary integrity under operating conditions </t>
+          <t xml:space="preserve">Contain process water under vacuum or stripping gas pressure </t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t xml:space="preserve">STD – Structural deficiency </t>
+          <t xml:space="preserve">STD - Structural deficiency </t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t xml:space="preserve">2.2 Corrosion </t>
+          <t xml:space="preserve">2.6 Fatigue </t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t xml:space="preserve">Chloride stress corrosion cracking at weld heat-affected zones </t>
+          <t xml:space="preserve">Thermal cycling causes cracking at nozzle-to-shell welds </t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t xml:space="preserve">PWHT documentation verification [Y/N]; Weld inspection campaign [Y/N] </t>
+          <t xml:space="preserve">NDT of critical welds performed? [Y/N] </t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
@@ -776,19 +776,19 @@
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t xml:space="preserve">Preventive; Predictive </t>
+          <t xml:space="preserve">Predictive </t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t xml:space="preserve">VEDA </t>
+          <t xml:space="preserve">VEDA - Dearator </t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t xml:space="preserve">Remove dissolved oxygen from seawater/process water by contacting with stripping gas or vacuum to meet process water quality specifications for corrosion control in injection systems </t>
+          <t xml:space="preserve">Remove dissolved oxygen from process water to prevent downstream corrosion </t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
@@ -798,27 +798,27 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t xml:space="preserve">Contain deaerated water and maintain pressure boundary integrity under operating conditions </t>
+          <t xml:space="preserve">Contain process water under vacuum or stripping gas pressure </t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t xml:space="preserve">ELP – External leakage – process medium </t>
+          <t xml:space="preserve">STD - Structural deficiency </t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t xml:space="preserve">2.2 Corrosion </t>
+          <t xml:space="preserve">1.4 Deformation </t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t xml:space="preserve">Pitting corrosion penetrates shell wall causing active water leakage </t>
+          <t xml:space="preserve">Vacuum-induced buckling from inadequate stiffening </t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t xml:space="preserve">External visual inspection for wet spots/rust trails [Y/N]; UT scanning of suspect areas [Y/N] </t>
+          <t xml:space="preserve">Column roundness and shell deformation checked? [Y/N] </t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
@@ -828,19 +828,19 @@
       </c>
       <c r="J8" t="inlineStr">
         <is>
-          <t xml:space="preserve">Preventive; Predictive </t>
+          <t xml:space="preserve">Preventive </t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t xml:space="preserve">VEDA </t>
+          <t xml:space="preserve">VEDA - Dearator </t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t xml:space="preserve">Remove dissolved oxygen from seawater/process water by contacting with stripping gas or vacuum to meet process water quality specifications for corrosion control in injection systems </t>
+          <t xml:space="preserve">Remove dissolved oxygen from process water to prevent downstream corrosion </t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
@@ -850,27 +850,27 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t xml:space="preserve">Contain deaerated water and maintain pressure boundary integrity under operating conditions </t>
+          <t xml:space="preserve">Contain process water under vacuum or stripping gas pressure </t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t xml:space="preserve">ELP – External leakage – process medium </t>
+          <t xml:space="preserve">PDE - Parameter deviation </t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t xml:space="preserve">2.5 Breakage </t>
+          <t xml:space="preserve">5.2 Contamination </t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t xml:space="preserve">Fatigue crack propagation through full wall thickness causes active leak </t>
+          <t xml:space="preserve">Internal scaling or biofouling alters deaeration efficiency </t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t xml:space="preserve">Weld joint NDT [Y/N]; Hydrostatic pressure test [Y/N] </t>
+          <t xml:space="preserve">Water outlet oxygen content within specification? [Y/N] </t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
@@ -880,19 +880,19 @@
       </c>
       <c r="J9" t="inlineStr">
         <is>
-          <t xml:space="preserve">Predictive; Failure-Finding </t>
+          <t xml:space="preserve">Predictive </t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t xml:space="preserve">VEDA </t>
+          <t xml:space="preserve">VEDA - Dearator </t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t xml:space="preserve">Remove dissolved oxygen from seawater/process water by contacting with stripping gas or vacuum to meet process water quality specifications for corrosion control in injection systems </t>
+          <t xml:space="preserve">Remove dissolved oxygen from process water to prevent downstream corrosion </t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
@@ -902,27 +902,27 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t xml:space="preserve">Contain deaerated water and maintain pressure boundary integrity under operating conditions </t>
+          <t xml:space="preserve">Contain process water under vacuum or stripping gas pressure </t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t xml:space="preserve">ELP – External leakage – process medium </t>
+          <t xml:space="preserve">PDE - Parameter deviation </t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t xml:space="preserve">1.4 Deformation </t>
+          <t xml:space="preserve">2.2 Corrosion </t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t xml:space="preserve">Gasket seating surface deformation at flanged connections </t>
+          <t xml:space="preserve">Internal rust formation contaminates product water </t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t xml:space="preserve">Flange face inspection [Y/N]; Bolt torque verification [Y/N] </t>
+          <t xml:space="preserve">Internal coating/lining condition inspected? [Y/N] </t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
@@ -932,19 +932,19 @@
       </c>
       <c r="J10" t="inlineStr">
         <is>
-          <t xml:space="preserve">Preventive; Preventive </t>
+          <t xml:space="preserve">Preventive </t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t xml:space="preserve">VEDA </t>
+          <t xml:space="preserve">VEDA - Dearator </t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t xml:space="preserve">Remove dissolved oxygen from seawater/process water by contacting with stripping gas or vacuum to meet process water quality specifications for corrosion control in injection systems </t>
+          <t xml:space="preserve">Remove dissolved oxygen from process water to prevent downstream corrosion </t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
@@ -954,27 +954,27 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t xml:space="preserve">Contain deaerated water and maintain pressure boundary integrity under operating conditions </t>
+          <t xml:space="preserve">Contain process water under vacuum or stripping gas pressure </t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t xml:space="preserve">VIB – Vibration </t>
+          <t xml:space="preserve">PDE - Parameter deviation </t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t xml:space="preserve">1.5 Looseness </t>
+          <t xml:space="preserve">1.3 Clearance/alignment failure </t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t xml:space="preserve">Foundation bolt loosening allows column movement under operational loads </t>
+          <t xml:space="preserve">Foundation movement causes column tilt affecting level control </t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t xml:space="preserve">Foundation bolt torque check [Y/N]; Visual inspection of supports [Y/N] </t>
+          <t xml:space="preserve">Column verticality and foundation settlement checked? [Y/N] </t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
@@ -984,19 +984,19 @@
       </c>
       <c r="J11" t="inlineStr">
         <is>
-          <t xml:space="preserve">Preventive; Preventive </t>
+          <t xml:space="preserve">Preventive </t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t xml:space="preserve">VEDA </t>
+          <t xml:space="preserve">VEDA - Dearator </t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t xml:space="preserve">Remove dissolved oxygen from seawater/process water by contacting with stripping gas or vacuum to meet process water quality specifications for corrosion control in injection systems </t>
+          <t xml:space="preserve">Remove dissolved oxygen from process water to prevent downstream corrosion </t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
@@ -1006,27 +1006,27 @@
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t xml:space="preserve">Contain deaerated water and maintain pressure boundary integrity under operating conditions </t>
+          <t xml:space="preserve">Contain process water under vacuum or stripping gas pressure </t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t xml:space="preserve">VIB – Vibration </t>
+          <t xml:space="preserve">NOI - Noise </t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t xml:space="preserve">2.6 Fatigue </t>
+          <t xml:space="preserve">2.2 Corrosion </t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t xml:space="preserve">Flow-induced vibration at natural frequency causes shell resonant vibration </t>
+          <t xml:space="preserve">Active corrosion pitting creates localized flow turbulence noise </t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t xml:space="preserve">Vibration monitoring survey [Y/N]; Flow rate check within design limits [Y/N] </t>
+          <t xml:space="preserve">Acoustic emission monitoring for corrosion performed? [Y/N] </t>
         </is>
       </c>
       <c r="I12" t="inlineStr">
@@ -1036,19 +1036,19 @@
       </c>
       <c r="J12" t="inlineStr">
         <is>
-          <t xml:space="preserve">Predictive; Preventive </t>
+          <t xml:space="preserve">Predictive </t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t xml:space="preserve">VEDA </t>
+          <t xml:space="preserve">VEDA - Dearator </t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t xml:space="preserve">Remove dissolved oxygen from seawater/process water by contacting with stripping gas or vacuum to meet process water quality specifications for corrosion control in injection systems </t>
+          <t xml:space="preserve">Remove dissolved oxygen from process water to prevent downstream corrosion </t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
@@ -1058,27 +1058,27 @@
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t xml:space="preserve">Contain deaerated water and maintain pressure boundary integrity under operating conditions </t>
+          <t xml:space="preserve">Contain process water under vacuum or stripping gas pressure </t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t xml:space="preserve">NOI – Noise </t>
+          <t xml:space="preserve">NOI - Noise </t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t xml:space="preserve">2.1 Cavitation </t>
+          <t xml:space="preserve">2.3 Erosion </t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t xml:space="preserve">Internal fluid cavitation at high velocity zones generates noise </t>
+          <t xml:space="preserve">Internal erosion creates turbulence generating abnormal noise </t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t xml:space="preserve">Pressure and flow monitoring within design envelope [Y/N]; Internal inspection for cavitation damage [Y/N] </t>
+          <t xml:space="preserve">Internal inspection for erosion damage performed? [Y/N] </t>
         </is>
       </c>
       <c r="I13" t="inlineStr">
@@ -1088,19 +1088,19 @@
       </c>
       <c r="J13" t="inlineStr">
         <is>
-          <t xml:space="preserve">Predictive; Preventive </t>
+          <t xml:space="preserve">Preventive </t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t xml:space="preserve">VEDA </t>
+          <t xml:space="preserve">VEDA - Dearator </t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t xml:space="preserve">Remove dissolved oxygen from seawater/process water by contacting with stripping gas or vacuum to meet process water quality specifications for corrosion control in injection systems </t>
+          <t xml:space="preserve">Remove dissolved oxygen from process water to prevent downstream corrosion </t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
@@ -1110,27 +1110,27 @@
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t xml:space="preserve">Contain deaerated water and maintain pressure boundary integrity under operating conditions </t>
+          <t xml:space="preserve">Contain process water under vacuum or stripping gas pressure </t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t xml:space="preserve">NOI – Noise </t>
+          <t xml:space="preserve">SBU - Sludge build-up </t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t xml:space="preserve">2.3 Erosion </t>
+          <t xml:space="preserve">5.2 Contamination </t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t xml:space="preserve">Internal erosion damage creates turbulent flow generating abnormal noise </t>
+          <t xml:space="preserve">Sediment and sludge accumulation in column bottom </t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t xml:space="preserve">Internal visual inspection for erosion damage [Y/N]; Flow velocity verification [Y/N] </t>
+          <t xml:space="preserve">Column bottom drain flushed and sludge level checked? [Y/N] </t>
         </is>
       </c>
       <c r="I14" t="inlineStr">
@@ -1140,19 +1140,19 @@
       </c>
       <c r="J14" t="inlineStr">
         <is>
-          <t xml:space="preserve">Predictive; Preventive </t>
+          <t xml:space="preserve">Preventive </t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t xml:space="preserve">VEDA </t>
+          <t xml:space="preserve">VEDA - Dearator </t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t xml:space="preserve">Remove dissolved oxygen from seawater/process water by contacting with stripping gas or vacuum to meet process water quality specifications for corrosion control in injection systems </t>
+          <t xml:space="preserve">Remove dissolved oxygen from process water to prevent downstream corrosion </t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
@@ -1162,27 +1162,27 @@
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t xml:space="preserve">Contain deaerated water and maintain pressure boundary integrity under operating conditions </t>
+          <t xml:space="preserve">Contain process water under vacuum or stripping gas pressure </t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t xml:space="preserve">OHE – Overheating </t>
+          <t xml:space="preserve">SBU - Sludge build-up </t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t xml:space="preserve">5.3 Miscellaneous external influences </t>
+          <t xml:space="preserve">2.2 Corrosion </t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t xml:space="preserve">External fire exposure or process upset causes shell temperature excursion </t>
+          <t xml:space="preserve">Corrosion by-products accelerate under-deposit corrosion </t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t xml:space="preserve">Temperature monitoring [Y/N]; Fireproofing condition check [Y/N] </t>
+          <t xml:space="preserve">Bottom sludge sample analyzed for corrosion products? [Y/N] </t>
         </is>
       </c>
       <c r="I15" t="inlineStr">
@@ -1192,19 +1192,19 @@
       </c>
       <c r="J15" t="inlineStr">
         <is>
-          <t xml:space="preserve">Predictive; Preventive </t>
+          <t xml:space="preserve">Predictive </t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t xml:space="preserve">VEDA </t>
+          <t xml:space="preserve">VEDA - Dearator </t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t xml:space="preserve">Remove dissolved oxygen from seawater/process water by contacting with stripping gas or vacuum to meet process water quality specifications for corrosion control in injection systems </t>
+          <t xml:space="preserve">Remove dissolved oxygen from process water to prevent downstream corrosion </t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
@@ -1214,39 +1214,4695 @@
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t xml:space="preserve">Contain deaerated water and maintain pressure boundary integrity under operating conditions </t>
+          <t xml:space="preserve">Contain process water under vacuum or stripping gas pressure </t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t xml:space="preserve">OHE – Overheating </t>
+          <t xml:space="preserve">VIB - Vibration </t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
+          <t xml:space="preserve">2.6 Fatigue </t>
+        </is>
+      </c>
+      <c r="G16" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Flow-induced vibration from stripping gas causes shell pulsation </t>
+        </is>
+      </c>
+      <c r="H16" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Column shell vibration monitoring performed? [Y/N] </t>
+        </is>
+      </c>
+      <c r="I16" t="inlineStr">
+        <is>
+          <t xml:space="preserve">TBD </t>
+        </is>
+      </c>
+      <c r="J16" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Predictive </t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t xml:space="preserve">VEDA - Dearator </t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Remove dissolved oxygen from process water to prevent downstream corrosion </t>
+        </is>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>Shell Failure</t>
+        </is>
+      </c>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Contain process water under vacuum or stripping gas pressure </t>
+        </is>
+      </c>
+      <c r="E17" t="inlineStr">
+        <is>
+          <t xml:space="preserve">VIB - Vibration </t>
+        </is>
+      </c>
+      <c r="F17" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1.3 Clearance/alignment failure </t>
+        </is>
+      </c>
+      <c r="G17" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Water hammer from pump startup transmits shock vibration </t>
+        </is>
+      </c>
+      <c r="H17" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Column inlet check valve operation verified? [Y/N] </t>
+        </is>
+      </c>
+      <c r="I17" t="inlineStr">
+        <is>
+          <t xml:space="preserve">TBD </t>
+        </is>
+      </c>
+      <c r="J17" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Failure-Finding </t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t xml:space="preserve">VEDA - Dearator </t>
+        </is>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Remove dissolved oxygen from process water to prevent downstream corrosion </t>
+        </is>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>Support/Skirt Failure *</t>
+        </is>
+      </c>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Support column weight and resist wind/seismic loads </t>
+        </is>
+      </c>
+      <c r="E18" t="inlineStr">
+        <is>
+          <t xml:space="preserve">STD - Structural deficiency </t>
+        </is>
+      </c>
+      <c r="F18" t="inlineStr">
+        <is>
           <t xml:space="preserve">2.2 Corrosion </t>
         </is>
       </c>
-      <c r="G16" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Internal scaling/insulation reduces heat dissipation causing localized hot spots </t>
-        </is>
-      </c>
-      <c r="H16" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Insulation condition check [Y/N]; External surface temperature survey [Y/N] </t>
-        </is>
-      </c>
-      <c r="I16" t="inlineStr">
-        <is>
-          <t xml:space="preserve">TBD </t>
-        </is>
-      </c>
-      <c r="J16" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Preventive; Predictive </t>
-        </is>
-      </c>
+      <c r="G18" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Skirt corrosion reduces load-bearing capacity </t>
+        </is>
+      </c>
+      <c r="H18" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Skirt-to-shell weld and support legs inspected for corrosion? [Y/N] </t>
+        </is>
+      </c>
+      <c r="I18" t="inlineStr">
+        <is>
+          <t xml:space="preserve">TBD </t>
+        </is>
+      </c>
+      <c r="J18" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Preventive </t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t xml:space="preserve">VEDA - Dearator </t>
+        </is>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Remove dissolved oxygen from process water to prevent downstream corrosion </t>
+        </is>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>Support/Skirt Failure *</t>
+        </is>
+      </c>
+      <c r="D19" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Support column weight and resist wind/seismic loads </t>
+        </is>
+      </c>
+      <c r="E19" t="inlineStr">
+        <is>
+          <t xml:space="preserve">STD - Structural deficiency </t>
+        </is>
+      </c>
+      <c r="F19" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2.6 Fatigue </t>
+        </is>
+      </c>
+      <c r="G19" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Wind/thermal cycling causes crack in skirt weld </t>
+        </is>
+      </c>
+      <c r="H19" t="inlineStr">
+        <is>
+          <t xml:space="preserve">NDT of skirt attachment weld performed? [Y/N] </t>
+        </is>
+      </c>
+      <c r="I19" t="inlineStr">
+        <is>
+          <t xml:space="preserve">TBD </t>
+        </is>
+      </c>
+      <c r="J19" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Predictive </t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t xml:space="preserve">VEDA - Dearator </t>
+        </is>
+      </c>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Remove dissolved oxygen from process water to prevent downstream corrosion </t>
+        </is>
+      </c>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>Support/Skirt Failure *</t>
+        </is>
+      </c>
+      <c r="D20" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Support column weight and resist wind/seismic loads </t>
+        </is>
+      </c>
+      <c r="E20" t="inlineStr">
+        <is>
+          <t xml:space="preserve">STD - Structural deficiency </t>
+        </is>
+      </c>
+      <c r="F20" t="inlineStr">
+        <is>
+          <t xml:space="preserve">5.3 Miscellaneous external influences </t>
+        </is>
+      </c>
+      <c r="G20" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Impact from dropped objects damages support </t>
+        </is>
+      </c>
+      <c r="H20" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Support structure free from visible damage? [Y/N] </t>
+        </is>
+      </c>
+      <c r="I20" t="inlineStr">
+        <is>
+          <t xml:space="preserve">TBD </t>
+        </is>
+      </c>
+      <c r="J20" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Preventive </t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t xml:space="preserve">VEDA - Dearator </t>
+        </is>
+      </c>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Remove dissolved oxygen from process water to prevent downstream corrosion </t>
+        </is>
+      </c>
+      <c r="C21" t="inlineStr">
+        <is>
+          <t>Support/Skirt Failure *</t>
+        </is>
+      </c>
+      <c r="D21" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Support column weight and resist wind/seismic loads </t>
+        </is>
+      </c>
+      <c r="E21" t="inlineStr">
+        <is>
+          <t xml:space="preserve">VIB - Vibration </t>
+        </is>
+      </c>
+      <c r="F21" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1.5 Looseness </t>
+        </is>
+      </c>
+      <c r="G21" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Anchor bolt loosening causes column instability </t>
+        </is>
+      </c>
+      <c r="H21" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Anchor bolts tightened to specified torque? [Y/N] </t>
+        </is>
+      </c>
+      <c r="I21" t="inlineStr">
+        <is>
+          <t xml:space="preserve">TBD </t>
+        </is>
+      </c>
+      <c r="J21" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Preventive </t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
+          <t xml:space="preserve">VEDA - Dearator </t>
+        </is>
+      </c>
+      <c r="B22" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Remove dissolved oxygen from process water to prevent downstream corrosion </t>
+        </is>
+      </c>
+      <c r="C22" t="inlineStr">
+        <is>
+          <t>Support/Skirt Failure *</t>
+        </is>
+      </c>
+      <c r="D22" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Support column weight and resist wind/seismic loads </t>
+        </is>
+      </c>
+      <c r="E22" t="inlineStr">
+        <is>
+          <t xml:space="preserve">VIB - Vibration </t>
+        </is>
+      </c>
+      <c r="F22" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1.3 Clearance/alignment failure </t>
+        </is>
+      </c>
+      <c r="G22" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Foundation settlement causes uneven loading and vibration </t>
+        </is>
+      </c>
+      <c r="H22" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Foundation settlement monitoring data reviewed? [Y/N] </t>
+        </is>
+      </c>
+      <c r="I22" t="inlineStr">
+        <is>
+          <t xml:space="preserve">TBD </t>
+        </is>
+      </c>
+      <c r="J22" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Predictive </t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="inlineStr">
+        <is>
+          <t xml:space="preserve">VEDA - Dearator </t>
+        </is>
+      </c>
+      <c r="B23" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Remove dissolved oxygen from process water to prevent downstream corrosion </t>
+        </is>
+      </c>
+      <c r="C23" t="inlineStr">
+        <is>
+          <t>Support/Skirt Failure *</t>
+        </is>
+      </c>
+      <c r="D23" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Support column weight and resist wind/seismic loads </t>
+        </is>
+      </c>
+      <c r="E23" t="inlineStr">
+        <is>
+          <t xml:space="preserve">VIB - Vibration </t>
+        </is>
+      </c>
+      <c r="F23" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2.6 Fatigue </t>
+        </is>
+      </c>
+      <c r="G23" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Vortex shedding from wind creates resonant vibration </t>
+        </is>
+      </c>
+      <c r="H23" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Wind-induced vibration analysis reviewed? [Y/N] </t>
+        </is>
+      </c>
+      <c r="I23" t="inlineStr">
+        <is>
+          <t xml:space="preserve">TBD </t>
+        </is>
+      </c>
+      <c r="J23" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Preventive </t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="inlineStr">
+        <is>
+          <t xml:space="preserve">VEDA - Dearator </t>
+        </is>
+      </c>
+      <c r="B24" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Remove dissolved oxygen from process water to prevent downstream corrosion </t>
+        </is>
+      </c>
+      <c r="C24" t="inlineStr">
+        <is>
+          <t>Support/Skirt Failure *</t>
+        </is>
+      </c>
+      <c r="D24" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Support column weight and resist wind/seismic loads </t>
+        </is>
+      </c>
+      <c r="E24" t="inlineStr">
+        <is>
+          <t xml:space="preserve">NOI - Noise </t>
+        </is>
+      </c>
+      <c r="F24" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1.5 Looseness </t>
+        </is>
+      </c>
+      <c r="G24" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Loose connections rattle under operational vibration </t>
+        </is>
+      </c>
+      <c r="H24" t="inlineStr">
+        <is>
+          <t xml:space="preserve">All bolted connections on support verified tight? [Y/N] </t>
+        </is>
+      </c>
+      <c r="I24" t="inlineStr">
+        <is>
+          <t xml:space="preserve">TBD </t>
+        </is>
+      </c>
+      <c r="J24" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Preventive </t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="inlineStr">
+        <is>
+          <t xml:space="preserve">VEDA - Dearator </t>
+        </is>
+      </c>
+      <c r="B25" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Remove dissolved oxygen from process water to prevent downstream corrosion </t>
+        </is>
+      </c>
+      <c r="C25" t="inlineStr">
+        <is>
+          <t>Support/Skirt Failure *</t>
+        </is>
+      </c>
+      <c r="D25" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Support column weight and resist wind/seismic loads </t>
+        </is>
+      </c>
+      <c r="E25" t="inlineStr">
+        <is>
+          <t xml:space="preserve">NOI - Noise </t>
+        </is>
+      </c>
+      <c r="F25" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2.6 Fatigue </t>
+        </is>
+      </c>
+      <c r="G25" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Fatigue crack propagation at attachments generates noise </t>
+        </is>
+      </c>
+      <c r="H25" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Visual inspection for cracks at support connections performed? [Y/N] </t>
+        </is>
+      </c>
+      <c r="I25" t="inlineStr">
+        <is>
+          <t xml:space="preserve">TBD </t>
+        </is>
+      </c>
+      <c r="J25" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Preventive </t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="inlineStr">
+        <is>
+          <t xml:space="preserve">VEDA - Dearator </t>
+        </is>
+      </c>
+      <c r="B26" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Remove dissolved oxygen from process water to prevent downstream corrosion </t>
+        </is>
+      </c>
+      <c r="C26" t="inlineStr">
+        <is>
+          <t>Support/Skirt Failure *</t>
+        </is>
+      </c>
+      <c r="D26" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Support column weight and resist wind/seismic loads </t>
+        </is>
+      </c>
+      <c r="E26" t="inlineStr">
+        <is>
+          <t xml:space="preserve">SLP - Slippage </t>
+        </is>
+      </c>
+      <c r="F26" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1.5 Looseness </t>
+        </is>
+      </c>
+      <c r="G26" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Loose anchor bolts allow column base to shift </t>
+        </is>
+      </c>
+      <c r="H26" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Column baseplate alignment checked against foundation marks? [Y/N] </t>
+        </is>
+      </c>
+      <c r="I26" t="inlineStr">
+        <is>
+          <t xml:space="preserve">TBD </t>
+        </is>
+      </c>
+      <c r="J26" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Preventive </t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="inlineStr">
+        <is>
+          <t xml:space="preserve">VEDA - Dearator </t>
+        </is>
+      </c>
+      <c r="B27" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Remove dissolved oxygen from process water to prevent downstream corrosion </t>
+        </is>
+      </c>
+      <c r="C27" t="inlineStr">
+        <is>
+          <t>Support/Skirt Failure *</t>
+        </is>
+      </c>
+      <c r="D27" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Support column weight and resist wind/seismic loads </t>
+        </is>
+      </c>
+      <c r="E27" t="inlineStr">
+        <is>
+          <t xml:space="preserve">SLP - Slippage </t>
+        </is>
+      </c>
+      <c r="F27" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1.4 Deformation </t>
+        </is>
+      </c>
+      <c r="G27" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Foundation settlement or heave causes baseplate deformation </t>
+        </is>
+      </c>
+      <c r="H27" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Grout condition at column base inspected? [Y/N] </t>
+        </is>
+      </c>
+      <c r="I27" t="inlineStr">
+        <is>
+          <t xml:space="preserve">TBD </t>
+        </is>
+      </c>
+      <c r="J27" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Preventive </t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="inlineStr">
+        <is>
+          <t xml:space="preserve">VEDA - Dearator </t>
+        </is>
+      </c>
+      <c r="B28" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Remove dissolved oxygen from process water to prevent downstream corrosion </t>
+        </is>
+      </c>
+      <c r="C28" t="inlineStr">
+        <is>
+          <t>Support/Skirt Failure *</t>
+        </is>
+      </c>
+      <c r="D28" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Support column weight and resist wind/seismic loads </t>
+        </is>
+      </c>
+      <c r="E28" t="inlineStr">
+        <is>
+          <t xml:space="preserve">PDE - Parameter deviation </t>
+        </is>
+      </c>
+      <c r="F28" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1.5 Looseness </t>
+        </is>
+      </c>
+      <c r="G28" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Loose support allows column tilt affecting level measurement </t>
+        </is>
+      </c>
+      <c r="H28" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Column verticality checked within acceptable tolerance? [Y/N] </t>
+        </is>
+      </c>
+      <c r="I28" t="inlineStr">
+        <is>
+          <t xml:space="preserve">TBD </t>
+        </is>
+      </c>
+      <c r="J28" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Preventive </t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="inlineStr">
+        <is>
+          <t xml:space="preserve">VEDA - Dearator </t>
+        </is>
+      </c>
+      <c r="B29" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Remove dissolved oxygen from process water to prevent downstream corrosion </t>
+        </is>
+      </c>
+      <c r="C29" t="inlineStr">
+        <is>
+          <t>Support/Skirt Failure *</t>
+        </is>
+      </c>
+      <c r="D29" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Support column weight and resist wind/seismic loads </t>
+        </is>
+      </c>
+      <c r="E29" t="inlineStr">
+        <is>
+          <t xml:space="preserve">PDE - Parameter deviation </t>
+        </is>
+      </c>
+      <c r="F29" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1.4 Deformation </t>
+        </is>
+      </c>
+      <c r="G29" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Foundation settlement causes nozzle misalignment straining piping </t>
+        </is>
+      </c>
+      <c r="H29" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Pipe strain on column nozzles verified acceptable? [Y/N] </t>
+        </is>
+      </c>
+      <c r="I29" t="inlineStr">
+        <is>
+          <t xml:space="preserve">TBD </t>
+        </is>
+      </c>
+      <c r="J29" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Preventive </t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="inlineStr">
+        <is>
+          <t xml:space="preserve">VEDA - Dearator </t>
+        </is>
+      </c>
+      <c r="B30" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Remove dissolved oxygen from process water to prevent downstream corrosion </t>
+        </is>
+      </c>
+      <c r="C30" t="inlineStr">
+        <is>
+          <t>Support/Skirt Failure *</t>
+        </is>
+      </c>
+      <c r="D30" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Support column weight and resist wind/seismic loads </t>
+        </is>
+      </c>
+      <c r="E30" t="inlineStr">
+        <is>
+          <t xml:space="preserve">SER - Minor in-service problems </t>
+        </is>
+      </c>
+      <c r="F30" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2.2 Corrosion </t>
+        </is>
+      </c>
+      <c r="G30" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Surface rust on support structure </t>
+        </is>
+      </c>
+      <c r="H30" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Support protective coating condition inspected? [Y/N] </t>
+        </is>
+      </c>
+      <c r="I30" t="inlineStr">
+        <is>
+          <t xml:space="preserve">TBD </t>
+        </is>
+      </c>
+      <c r="J30" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Preventive </t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="inlineStr">
+        <is>
+          <t xml:space="preserve">VEDA - Dearator </t>
+        </is>
+      </c>
+      <c r="B31" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Remove dissolved oxygen from process water to prevent downstream corrosion </t>
+        </is>
+      </c>
+      <c r="C31" t="inlineStr">
+        <is>
+          <t>Support/Skirt Failure *</t>
+        </is>
+      </c>
+      <c r="D31" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Support column weight and resist wind/seismic loads </t>
+        </is>
+      </c>
+      <c r="E31" t="inlineStr">
+        <is>
+          <t xml:space="preserve">SER - Minor in-service problems </t>
+        </is>
+      </c>
+      <c r="F31" t="inlineStr">
+        <is>
+          <t xml:space="preserve">5.3 Miscellaneous external influences </t>
+        </is>
+      </c>
+      <c r="G31" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Minor dents from maintenance activities </t>
+        </is>
+      </c>
+      <c r="H31" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Support structure free from significant damage? [Y/N] </t>
+        </is>
+      </c>
+      <c r="I31" t="inlineStr">
+        <is>
+          <t xml:space="preserve">TBD </t>
+        </is>
+      </c>
+      <c r="J31" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Preventive </t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="inlineStr">
+        <is>
+          <t xml:space="preserve">VEDA - Dearator </t>
+        </is>
+      </c>
+      <c r="B32" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Remove dissolved oxygen from process water to prevent downstream corrosion </t>
+        </is>
+      </c>
+      <c r="C32" t="inlineStr">
+        <is>
+          <t>Inlet Nozzle Failure *</t>
+        </is>
+      </c>
+      <c r="D32" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Allow incoming water to enter column with minimal turbulence </t>
+        </is>
+      </c>
+      <c r="E32" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ELP - External leakage - process medium </t>
+        </is>
+      </c>
+      <c r="F32" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2.2 Corrosion </t>
+        </is>
+      </c>
+      <c r="G32" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Corrosion at nozzle-to-shell weld or flange causes water leak </t>
+        </is>
+      </c>
+      <c r="H32" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Nozzle-to-shell weld inspected for corrosion? [Y/N] </t>
+        </is>
+      </c>
+      <c r="I32" t="inlineStr">
+        <is>
+          <t xml:space="preserve">TBD </t>
+        </is>
+      </c>
+      <c r="J32" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Preventive </t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="inlineStr">
+        <is>
+          <t xml:space="preserve">VEDA - Dearator </t>
+        </is>
+      </c>
+      <c r="B33" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Remove dissolved oxygen from process water to prevent downstream corrosion </t>
+        </is>
+      </c>
+      <c r="C33" t="inlineStr">
+        <is>
+          <t>Inlet Nozzle Failure *</t>
+        </is>
+      </c>
+      <c r="D33" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Allow incoming water to enter column with minimal turbulence </t>
+        </is>
+      </c>
+      <c r="E33" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ELP - External leakage - process medium </t>
+        </is>
+      </c>
+      <c r="F33" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2.6 Fatigue </t>
+        </is>
+      </c>
+      <c r="G33" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Thermal expansion cycling at flange causes gasket failure </t>
+        </is>
+      </c>
+      <c r="H33" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Flange bolts torque verified to specification? [Y/N] </t>
+        </is>
+      </c>
+      <c r="I33" t="inlineStr">
+        <is>
+          <t xml:space="preserve">TBD </t>
+        </is>
+      </c>
+      <c r="J33" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Preventive </t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="inlineStr">
+        <is>
+          <t xml:space="preserve">VEDA - Dearator </t>
+        </is>
+      </c>
+      <c r="B34" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Remove dissolved oxygen from process water to prevent downstream corrosion </t>
+        </is>
+      </c>
+      <c r="C34" t="inlineStr">
+        <is>
+          <t>Inlet Nozzle Failure *</t>
+        </is>
+      </c>
+      <c r="D34" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Allow incoming water to enter column with minimal turbulence </t>
+        </is>
+      </c>
+      <c r="E34" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ELP - External leakage - process medium </t>
+        </is>
+      </c>
+      <c r="F34" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2.3 Erosion </t>
+        </is>
+      </c>
+      <c r="G34" t="inlineStr">
+        <is>
+          <t xml:space="preserve">High-velocity water erodes nozzle internal wall </t>
+        </is>
+      </c>
+      <c r="H34" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Nozzle wall thickness measured by UT? [Y/N] </t>
+        </is>
+      </c>
+      <c r="I34" t="inlineStr">
+        <is>
+          <t xml:space="preserve">TBD </t>
+        </is>
+      </c>
+      <c r="J34" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Predictive </t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" t="inlineStr">
+        <is>
+          <t xml:space="preserve">VEDA - Dearator </t>
+        </is>
+      </c>
+      <c r="B35" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Remove dissolved oxygen from process water to prevent downstream corrosion </t>
+        </is>
+      </c>
+      <c r="C35" t="inlineStr">
+        <is>
+          <t>Inlet Nozzle Failure *</t>
+        </is>
+      </c>
+      <c r="D35" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Allow incoming water to enter column with minimal turbulence </t>
+        </is>
+      </c>
+      <c r="E35" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ELP - External leakage - process medium </t>
+        </is>
+      </c>
+      <c r="F35" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1.4 Deformation </t>
+        </is>
+      </c>
+      <c r="G35" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Flange gasket deformation from overtightening </t>
+        </is>
+      </c>
+      <c r="H35" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Nozzle flange gasket condition verified? [Y/N] </t>
+        </is>
+      </c>
+      <c r="I35" t="inlineStr">
+        <is>
+          <t xml:space="preserve">TBD </t>
+        </is>
+      </c>
+      <c r="J35" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Preventive </t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" t="inlineStr">
+        <is>
+          <t xml:space="preserve">VEDA - Dearator </t>
+        </is>
+      </c>
+      <c r="B36" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Remove dissolved oxygen from process water to prevent downstream corrosion </t>
+        </is>
+      </c>
+      <c r="C36" t="inlineStr">
+        <is>
+          <t>Inlet Nozzle Failure *</t>
+        </is>
+      </c>
+      <c r="D36" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Allow incoming water to enter column with minimal turbulence </t>
+        </is>
+      </c>
+      <c r="E36" t="inlineStr">
+        <is>
+          <t xml:space="preserve">PLU - Plugged/choked </t>
+        </is>
+      </c>
+      <c r="F36" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2.2 Corrosion </t>
+        </is>
+      </c>
+      <c r="G36" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Corrosion products accumulate restricting flow area </t>
+        </is>
+      </c>
+      <c r="H36" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Inlet nozzle internal condition inspected? [Y/N] </t>
+        </is>
+      </c>
+      <c r="I36" t="inlineStr">
+        <is>
+          <t xml:space="preserve">TBD </t>
+        </is>
+      </c>
+      <c r="J36" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Preventive </t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" t="inlineStr">
+        <is>
+          <t xml:space="preserve">VEDA - Dearator </t>
+        </is>
+      </c>
+      <c r="B37" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Remove dissolved oxygen from process water to prevent downstream corrosion </t>
+        </is>
+      </c>
+      <c r="C37" t="inlineStr">
+        <is>
+          <t>Inlet Nozzle Failure *</t>
+        </is>
+      </c>
+      <c r="D37" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Allow incoming water to enter column with minimal turbulence </t>
+        </is>
+      </c>
+      <c r="E37" t="inlineStr">
+        <is>
+          <t xml:space="preserve">PLU - Plugged/choked </t>
+        </is>
+      </c>
+      <c r="F37" t="inlineStr">
+        <is>
+          <t xml:space="preserve">5.2 Contamination </t>
+        </is>
+      </c>
+      <c r="G37" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Marine growth or fouling inside nozzle restricts flow </t>
+        </is>
+      </c>
+      <c r="H37" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Inlet strainer/filter differential pressure checked? [Y/N] </t>
+        </is>
+      </c>
+      <c r="I37" t="inlineStr">
+        <is>
+          <t xml:space="preserve">TBD </t>
+        </is>
+      </c>
+      <c r="J37" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Predictive </t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" t="inlineStr">
+        <is>
+          <t xml:space="preserve">VEDA - Dearator </t>
+        </is>
+      </c>
+      <c r="B38" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Remove dissolved oxygen from process water to prevent downstream corrosion </t>
+        </is>
+      </c>
+      <c r="C38" t="inlineStr">
+        <is>
+          <t>Inlet Nozzle Failure *</t>
+        </is>
+      </c>
+      <c r="D38" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Allow incoming water to enter column with minimal turbulence </t>
+        </is>
+      </c>
+      <c r="E38" t="inlineStr">
+        <is>
+          <t xml:space="preserve">STD - Structural deficiency </t>
+        </is>
+      </c>
+      <c r="F38" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2.2 Corrosion </t>
+        </is>
+      </c>
+      <c r="G38" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Wall thinning reduces nozzle pressure rating </t>
+        </is>
+      </c>
+      <c r="H38" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Nozzle minimum wall thickness verified? [Y/N] </t>
+        </is>
+      </c>
+      <c r="I38" t="inlineStr">
+        <is>
+          <t xml:space="preserve">TBD </t>
+        </is>
+      </c>
+      <c r="J38" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Predictive </t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" t="inlineStr">
+        <is>
+          <t xml:space="preserve">VEDA - Dearator </t>
+        </is>
+      </c>
+      <c r="B39" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Remove dissolved oxygen from process water to prevent downstream corrosion </t>
+        </is>
+      </c>
+      <c r="C39" t="inlineStr">
+        <is>
+          <t>Inlet Nozzle Failure *</t>
+        </is>
+      </c>
+      <c r="D39" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Allow incoming water to enter column with minimal turbulence </t>
+        </is>
+      </c>
+      <c r="E39" t="inlineStr">
+        <is>
+          <t xml:space="preserve">STD - Structural deficiency </t>
+        </is>
+      </c>
+      <c r="F39" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1.4 Deformation </t>
+        </is>
+      </c>
+      <c r="G39" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Mechanical impact damages nozzle structure </t>
+        </is>
+      </c>
+      <c r="H39" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Nozzle free from visible damage or deformation? [Y/N] </t>
+        </is>
+      </c>
+      <c r="I39" t="inlineStr">
+        <is>
+          <t xml:space="preserve">TBD </t>
+        </is>
+      </c>
+      <c r="J39" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Preventive </t>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" t="inlineStr">
+        <is>
+          <t xml:space="preserve">VEDA - Dearator </t>
+        </is>
+      </c>
+      <c r="B40" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Remove dissolved oxygen from process water to prevent downstream corrosion </t>
+        </is>
+      </c>
+      <c r="C40" t="inlineStr">
+        <is>
+          <t>Inlet Nozzle Failure *</t>
+        </is>
+      </c>
+      <c r="D40" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Allow incoming water to enter column with minimal turbulence </t>
+        </is>
+      </c>
+      <c r="E40" t="inlineStr">
+        <is>
+          <t xml:space="preserve">PDE - Parameter deviation </t>
+        </is>
+      </c>
+      <c r="F40" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2.2 Corrosion </t>
+        </is>
+      </c>
+      <c r="G40" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Internal corrosion creates rough surface affecting flow </t>
+        </is>
+      </c>
+      <c r="H40" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Inlet nozzle internal surface condition inspected? [Y/N] </t>
+        </is>
+      </c>
+      <c r="I40" t="inlineStr">
+        <is>
+          <t xml:space="preserve">TBD </t>
+        </is>
+      </c>
+      <c r="J40" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Preventive </t>
+        </is>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" t="inlineStr">
+        <is>
+          <t xml:space="preserve">VEDA - Dearator </t>
+        </is>
+      </c>
+      <c r="B41" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Remove dissolved oxygen from process water to prevent downstream corrosion </t>
+        </is>
+      </c>
+      <c r="C41" t="inlineStr">
+        <is>
+          <t>Inlet Nozzle Failure *</t>
+        </is>
+      </c>
+      <c r="D41" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Allow incoming water to enter column with minimal turbulence </t>
+        </is>
+      </c>
+      <c r="E41" t="inlineStr">
+        <is>
+          <t xml:space="preserve">PDE - Parameter deviation </t>
+        </is>
+      </c>
+      <c r="F41" t="inlineStr">
+        <is>
+          <t xml:space="preserve">5.2 Contamination </t>
+        </is>
+      </c>
+      <c r="G41" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Partial fouling reduces effective flow diameter </t>
+        </is>
+      </c>
+      <c r="H41" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Inlet pressure gauge reading within normal range? [Y/N] </t>
+        </is>
+      </c>
+      <c r="I41" t="inlineStr">
+        <is>
+          <t xml:space="preserve">TBD </t>
+        </is>
+      </c>
+      <c r="J41" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Predictive </t>
+        </is>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" t="inlineStr">
+        <is>
+          <t xml:space="preserve">VEDA - Dearator </t>
+        </is>
+      </c>
+      <c r="B42" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Remove dissolved oxygen from process water to prevent downstream corrosion </t>
+        </is>
+      </c>
+      <c r="C42" t="inlineStr">
+        <is>
+          <t>Inlet Nozzle Failure *</t>
+        </is>
+      </c>
+      <c r="D42" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Allow incoming water to enter column with minimal turbulence </t>
+        </is>
+      </c>
+      <c r="E42" t="inlineStr">
+        <is>
+          <t xml:space="preserve">VIB - Vibration </t>
+        </is>
+      </c>
+      <c r="F42" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2.3 Erosion </t>
+        </is>
+      </c>
+      <c r="G42" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Erosion damage creates flow disturbance causing vibration </t>
+        </is>
+      </c>
+      <c r="H42" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Inlet nozzle vibration levels monitored? [Y/N] </t>
+        </is>
+      </c>
+      <c r="I42" t="inlineStr">
+        <is>
+          <t xml:space="preserve">TBD </t>
+        </is>
+      </c>
+      <c r="J42" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Predictive </t>
+        </is>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" t="inlineStr">
+        <is>
+          <t xml:space="preserve">VEDA - Dearator </t>
+        </is>
+      </c>
+      <c r="B43" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Remove dissolved oxygen from process water to prevent downstream corrosion </t>
+        </is>
+      </c>
+      <c r="C43" t="inlineStr">
+        <is>
+          <t>Inlet Nozzle Failure *</t>
+        </is>
+      </c>
+      <c r="D43" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Allow incoming water to enter column with minimal turbulence </t>
+        </is>
+      </c>
+      <c r="E43" t="inlineStr">
+        <is>
+          <t xml:space="preserve">VIB - Vibration </t>
+        </is>
+      </c>
+      <c r="F43" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1.3 Clearance/alignment failure </t>
+        </is>
+      </c>
+      <c r="G43" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Nozzle-piping misalignment induces mechanical vibration </t>
+        </is>
+      </c>
+      <c r="H43" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Nozzle-piping alignment verified after maintenance? [Y/N] </t>
+        </is>
+      </c>
+      <c r="I43" t="inlineStr">
+        <is>
+          <t xml:space="preserve">TBD </t>
+        </is>
+      </c>
+      <c r="J43" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Preventive </t>
+        </is>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" t="inlineStr">
+        <is>
+          <t xml:space="preserve">VEDA - Dearator </t>
+        </is>
+      </c>
+      <c r="B44" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Remove dissolved oxygen from process water to prevent downstream corrosion </t>
+        </is>
+      </c>
+      <c r="C44" t="inlineStr">
+        <is>
+          <t>Inlet Nozzle Failure *</t>
+        </is>
+      </c>
+      <c r="D44" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Allow incoming water to enter column with minimal turbulence </t>
+        </is>
+      </c>
+      <c r="E44" t="inlineStr">
+        <is>
+          <t xml:space="preserve">NOI - Noise </t>
+        </is>
+      </c>
+      <c r="F44" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2.3 Erosion </t>
+        </is>
+      </c>
+      <c r="G44" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Erosion creates turbulence generating flow noise </t>
+        </is>
+      </c>
+      <c r="H44" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Inlet nozzle internal inspected for erosion? [Y/N] </t>
+        </is>
+      </c>
+      <c r="I44" t="inlineStr">
+        <is>
+          <t xml:space="preserve">TBD </t>
+        </is>
+      </c>
+      <c r="J44" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Preventive </t>
+        </is>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" t="inlineStr">
+        <is>
+          <t xml:space="preserve">VEDA - Dearator </t>
+        </is>
+      </c>
+      <c r="B45" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Remove dissolved oxygen from process water to prevent downstream corrosion </t>
+        </is>
+      </c>
+      <c r="C45" t="inlineStr">
+        <is>
+          <t>Inlet Nozzle Failure *</t>
+        </is>
+      </c>
+      <c r="D45" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Allow incoming water to enter column with minimal turbulence </t>
+        </is>
+      </c>
+      <c r="E45" t="inlineStr">
+        <is>
+          <t xml:space="preserve">NOI - Noise </t>
+        </is>
+      </c>
+      <c r="F45" t="inlineStr">
+        <is>
+          <t xml:space="preserve">5.2 Contamination </t>
+        </is>
+      </c>
+      <c r="G45" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Partial blockage causes flow restriction noise </t>
+        </is>
+      </c>
+      <c r="H45" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Inlet line checked for abnormal noise during operation? [Y/N] </t>
+        </is>
+      </c>
+      <c r="I45" t="inlineStr">
+        <is>
+          <t xml:space="preserve">TBD </t>
+        </is>
+      </c>
+      <c r="J45" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Predictive </t>
+        </is>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" t="inlineStr">
+        <is>
+          <t xml:space="preserve">VEDA - Dearator </t>
+        </is>
+      </c>
+      <c r="B46" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Remove dissolved oxygen from process water to prevent downstream corrosion </t>
+        </is>
+      </c>
+      <c r="C46" t="inlineStr">
+        <is>
+          <t>Outlet Nozzle Failure *</t>
+        </is>
+      </c>
+      <c r="D46" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Allow deaerated water to exit column to downstream equipment </t>
+        </is>
+      </c>
+      <c r="E46" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ELP - External leakage - process medium </t>
+        </is>
+      </c>
+      <c r="F46" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2.2 Corrosion </t>
+        </is>
+      </c>
+      <c r="G46" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Corrosion degradation of outlet nozzle causes water leak </t>
+        </is>
+      </c>
+      <c r="H46" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Outlet nozzle ultrasonic thickness measurement performed? [Y/N] </t>
+        </is>
+      </c>
+      <c r="I46" t="inlineStr">
+        <is>
+          <t xml:space="preserve">TBD </t>
+        </is>
+      </c>
+      <c r="J46" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Predictive </t>
+        </is>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" t="inlineStr">
+        <is>
+          <t xml:space="preserve">VEDA - Dearator </t>
+        </is>
+      </c>
+      <c r="B47" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Remove dissolved oxygen from process water to prevent downstream corrosion </t>
+        </is>
+      </c>
+      <c r="C47" t="inlineStr">
+        <is>
+          <t>Outlet Nozzle Failure *</t>
+        </is>
+      </c>
+      <c r="D47" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Allow deaerated water to exit column to downstream equipment </t>
+        </is>
+      </c>
+      <c r="E47" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ELP - External leakage - process medium </t>
+        </is>
+      </c>
+      <c r="F47" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2.3 Erosion </t>
+        </is>
+      </c>
+      <c r="G47" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Cavitating flow at pump suction erodes nozzle wall </t>
+        </is>
+      </c>
+      <c r="H47" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Outlet nozzle wall thickness verified? [Y/N] </t>
+        </is>
+      </c>
+      <c r="I47" t="inlineStr">
+        <is>
+          <t xml:space="preserve">TBD </t>
+        </is>
+      </c>
+      <c r="J47" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Predictive </t>
+        </is>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" t="inlineStr">
+        <is>
+          <t xml:space="preserve">VEDA - Dearator </t>
+        </is>
+      </c>
+      <c r="B48" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Remove dissolved oxygen from process water to prevent downstream corrosion </t>
+        </is>
+      </c>
+      <c r="C48" t="inlineStr">
+        <is>
+          <t>Outlet Nozzle Failure *</t>
+        </is>
+      </c>
+      <c r="D48" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Allow deaerated water to exit column to downstream equipment </t>
+        </is>
+      </c>
+      <c r="E48" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ELP - External leakage - process medium </t>
+        </is>
+      </c>
+      <c r="F48" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2.6 Fatigue </t>
+        </is>
+      </c>
+      <c r="G48" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Piping vibration transmitted to nozzle causes fatigue crack </t>
+        </is>
+      </c>
+      <c r="H48" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Outlet nozzle support and piping flexibility verified? [Y/N] </t>
+        </is>
+      </c>
+      <c r="I48" t="inlineStr">
+        <is>
+          <t xml:space="preserve">TBD </t>
+        </is>
+      </c>
+      <c r="J48" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Preventive </t>
+        </is>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" t="inlineStr">
+        <is>
+          <t xml:space="preserve">VEDA - Dearator </t>
+        </is>
+      </c>
+      <c r="B49" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Remove dissolved oxygen from process water to prevent downstream corrosion </t>
+        </is>
+      </c>
+      <c r="C49" t="inlineStr">
+        <is>
+          <t>Outlet Nozzle Failure *</t>
+        </is>
+      </c>
+      <c r="D49" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Allow deaerated water to exit column to downstream equipment </t>
+        </is>
+      </c>
+      <c r="E49" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ELP - External leakage - process medium </t>
+        </is>
+      </c>
+      <c r="F49" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1.4 Deformation </t>
+        </is>
+      </c>
+      <c r="G49" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Flange gasket failure from over-torquing </t>
+        </is>
+      </c>
+      <c r="H49" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Flange gasket condition checked on assembly? [Y/N] </t>
+        </is>
+      </c>
+      <c r="I49" t="inlineStr">
+        <is>
+          <t xml:space="preserve">TBD </t>
+        </is>
+      </c>
+      <c r="J49" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Preventive </t>
+        </is>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" t="inlineStr">
+        <is>
+          <t xml:space="preserve">VEDA - Dearator </t>
+        </is>
+      </c>
+      <c r="B50" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Remove dissolved oxygen from process water to prevent downstream corrosion </t>
+        </is>
+      </c>
+      <c r="C50" t="inlineStr">
+        <is>
+          <t>Outlet Nozzle Failure *</t>
+        </is>
+      </c>
+      <c r="D50" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Allow deaerated water to exit column to downstream equipment </t>
+        </is>
+      </c>
+      <c r="E50" t="inlineStr">
+        <is>
+          <t xml:space="preserve">PLU - Plugged/choked </t>
+        </is>
+      </c>
+      <c r="F50" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2.2 Corrosion </t>
+        </is>
+      </c>
+      <c r="G50" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Corrosion debris accumulates restricting outlet flow </t>
+        </is>
+      </c>
+      <c r="H50" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Outlet flow and differential pressure within normal range? [Y/N] </t>
+        </is>
+      </c>
+      <c r="I50" t="inlineStr">
+        <is>
+          <t xml:space="preserve">TBD </t>
+        </is>
+      </c>
+      <c r="J50" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Predictive </t>
+        </is>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" t="inlineStr">
+        <is>
+          <t xml:space="preserve">VEDA - Dearator </t>
+        </is>
+      </c>
+      <c r="B51" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Remove dissolved oxygen from process water to prevent downstream corrosion </t>
+        </is>
+      </c>
+      <c r="C51" t="inlineStr">
+        <is>
+          <t>Outlet Nozzle Failure *</t>
+        </is>
+      </c>
+      <c r="D51" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Allow deaerated water to exit column to downstream equipment </t>
+        </is>
+      </c>
+      <c r="E51" t="inlineStr">
+        <is>
+          <t xml:space="preserve">PLU - Plugged/choked </t>
+        </is>
+      </c>
+      <c r="F51" t="inlineStr">
+        <is>
+          <t xml:space="preserve">5.2 Contamination </t>
+        </is>
+      </c>
+      <c r="G51" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Internal fouling restricts flow area </t>
+        </is>
+      </c>
+      <c r="H51" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Outlet nozzle internal condition inspected during shutdown? [Y/N] </t>
+        </is>
+      </c>
+      <c r="I51" t="inlineStr">
+        <is>
+          <t xml:space="preserve">TBD </t>
+        </is>
+      </c>
+      <c r="J51" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Preventive </t>
+        </is>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" t="inlineStr">
+        <is>
+          <t xml:space="preserve">VEDA - Dearator </t>
+        </is>
+      </c>
+      <c r="B52" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Remove dissolved oxygen from process water to prevent downstream corrosion </t>
+        </is>
+      </c>
+      <c r="C52" t="inlineStr">
+        <is>
+          <t>Outlet Nozzle Failure *</t>
+        </is>
+      </c>
+      <c r="D52" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Allow deaerated water to exit column to downstream equipment </t>
+        </is>
+      </c>
+      <c r="E52" t="inlineStr">
+        <is>
+          <t xml:space="preserve">STD - Structural deficiency </t>
+        </is>
+      </c>
+      <c r="F52" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2.2 Corrosion </t>
+        </is>
+      </c>
+      <c r="G52" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Wall thinning reduces mechanical integrity </t>
+        </is>
+      </c>
+      <c r="H52" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Outlet nozzle remaining wall thickness within code allowance? [Y/N] </t>
+        </is>
+      </c>
+      <c r="I52" t="inlineStr">
+        <is>
+          <t xml:space="preserve">TBD </t>
+        </is>
+      </c>
+      <c r="J52" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Predictive </t>
+        </is>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" t="inlineStr">
+        <is>
+          <t xml:space="preserve">VEDA - Dearator </t>
+        </is>
+      </c>
+      <c r="B53" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Remove dissolved oxygen from process water to prevent downstream corrosion </t>
+        </is>
+      </c>
+      <c r="C53" t="inlineStr">
+        <is>
+          <t>Outlet Nozzle Failure *</t>
+        </is>
+      </c>
+      <c r="D53" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Allow deaerated water to exit column to downstream equipment </t>
+        </is>
+      </c>
+      <c r="E53" t="inlineStr">
+        <is>
+          <t xml:space="preserve">STD - Structural deficiency </t>
+        </is>
+      </c>
+      <c r="F53" t="inlineStr">
+        <is>
+          <t xml:space="preserve">5.3 Miscellaneous external influences </t>
+        </is>
+      </c>
+      <c r="G53" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Mechanical damage from dropped objects </t>
+        </is>
+      </c>
+      <c r="H53" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Outlet nozzle free from visible damage? [Y/N] </t>
+        </is>
+      </c>
+      <c r="I53" t="inlineStr">
+        <is>
+          <t xml:space="preserve">TBD </t>
+        </is>
+      </c>
+      <c r="J53" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Preventive </t>
+        </is>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" t="inlineStr">
+        <is>
+          <t xml:space="preserve">VEDA - Dearator </t>
+        </is>
+      </c>
+      <c r="B54" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Remove dissolved oxygen from process water to prevent downstream corrosion </t>
+        </is>
+      </c>
+      <c r="C54" t="inlineStr">
+        <is>
+          <t>Outlet Nozzle Failure *</t>
+        </is>
+      </c>
+      <c r="D54" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Allow deaerated water to exit column to downstream equipment </t>
+        </is>
+      </c>
+      <c r="E54" t="inlineStr">
+        <is>
+          <t xml:space="preserve">PDE - Parameter deviation </t>
+        </is>
+      </c>
+      <c r="F54" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2.2 Corrosion </t>
+        </is>
+      </c>
+      <c r="G54" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Internal corrosion increases friction affecting flow </t>
+        </is>
+      </c>
+      <c r="H54" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Outlet nozzle internal condition inspected? [Y/N] </t>
+        </is>
+      </c>
+      <c r="I54" t="inlineStr">
+        <is>
+          <t xml:space="preserve">TBD </t>
+        </is>
+      </c>
+      <c r="J54" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Preventive </t>
+        </is>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" t="inlineStr">
+        <is>
+          <t xml:space="preserve">VEDA - Dearator </t>
+        </is>
+      </c>
+      <c r="B55" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Remove dissolved oxygen from process water to prevent downstream corrosion </t>
+        </is>
+      </c>
+      <c r="C55" t="inlineStr">
+        <is>
+          <t>Outlet Nozzle Failure *</t>
+        </is>
+      </c>
+      <c r="D55" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Allow deaerated water to exit column to downstream equipment </t>
+        </is>
+      </c>
+      <c r="E55" t="inlineStr">
+        <is>
+          <t xml:space="preserve">PDE - Parameter deviation </t>
+        </is>
+      </c>
+      <c r="F55" t="inlineStr">
+        <is>
+          <t xml:space="preserve">5.2 Contamination </t>
+        </is>
+      </c>
+      <c r="G55" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Partial fouling restricts flow causing higher outlet pressure </t>
+        </is>
+      </c>
+      <c r="H55" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Outlet water pressure and flow compared to design? [Y/N] </t>
+        </is>
+      </c>
+      <c r="I55" t="inlineStr">
+        <is>
+          <t xml:space="preserve">TBD </t>
+        </is>
+      </c>
+      <c r="J55" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Predictive </t>
+        </is>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" t="inlineStr">
+        <is>
+          <t xml:space="preserve">VEDA - Dearator </t>
+        </is>
+      </c>
+      <c r="B56" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Remove dissolved oxygen from process water to prevent downstream corrosion </t>
+        </is>
+      </c>
+      <c r="C56" t="inlineStr">
+        <is>
+          <t>Outlet Nozzle Failure *</t>
+        </is>
+      </c>
+      <c r="D56" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Allow deaerated water to exit column to downstream equipment </t>
+        </is>
+      </c>
+      <c r="E56" t="inlineStr">
+        <is>
+          <t xml:space="preserve">VIB - Vibration </t>
+        </is>
+      </c>
+      <c r="F56" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2.3 Erosion </t>
+        </is>
+      </c>
+      <c r="G56" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Erosion damage creates turbulence inducing vibration </t>
+        </is>
+      </c>
+      <c r="H56" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Outlet nozzle vibration monitoring performed? [Y/N] </t>
+        </is>
+      </c>
+      <c r="I56" t="inlineStr">
+        <is>
+          <t xml:space="preserve">TBD </t>
+        </is>
+      </c>
+      <c r="J56" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Predictive </t>
+        </is>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" t="inlineStr">
+        <is>
+          <t xml:space="preserve">VEDA - Dearator </t>
+        </is>
+      </c>
+      <c r="B57" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Remove dissolved oxygen from process water to prevent downstream corrosion </t>
+        </is>
+      </c>
+      <c r="C57" t="inlineStr">
+        <is>
+          <t>Outlet Nozzle Failure *</t>
+        </is>
+      </c>
+      <c r="D57" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Allow deaerated water to exit column to downstream equipment </t>
+        </is>
+      </c>
+      <c r="E57" t="inlineStr">
+        <is>
+          <t xml:space="preserve">VIB - Vibration </t>
+        </is>
+      </c>
+      <c r="F57" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1.3 Clearance/alignment failure </t>
+        </is>
+      </c>
+      <c r="G57" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Nozzle-piping misalignment induces vibration </t>
+        </is>
+      </c>
+      <c r="H57" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Piping stress/alignment at outlet nozzle verified? [Y/N] </t>
+        </is>
+      </c>
+      <c r="I57" t="inlineStr">
+        <is>
+          <t xml:space="preserve">TBD </t>
+        </is>
+      </c>
+      <c r="J57" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Preventive </t>
+        </is>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" t="inlineStr">
+        <is>
+          <t xml:space="preserve">VEDA - Dearator </t>
+        </is>
+      </c>
+      <c r="B58" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Remove dissolved oxygen from process water to prevent downstream corrosion </t>
+        </is>
+      </c>
+      <c r="C58" t="inlineStr">
+        <is>
+          <t>Outlet Nozzle Failure *</t>
+        </is>
+      </c>
+      <c r="D58" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Allow deaerated water to exit column to downstream equipment </t>
+        </is>
+      </c>
+      <c r="E58" t="inlineStr">
+        <is>
+          <t xml:space="preserve">NOI - Noise </t>
+        </is>
+      </c>
+      <c r="F58" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2.3 Erosion </t>
+        </is>
+      </c>
+      <c r="G58" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Erosion pitting creates turbulence causing noise </t>
+        </is>
+      </c>
+      <c r="H58" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Outlet nozzle inspected for erosion during shutdown? [Y/N] </t>
+        </is>
+      </c>
+      <c r="I58" t="inlineStr">
+        <is>
+          <t xml:space="preserve">TBD </t>
+        </is>
+      </c>
+      <c r="J58" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Preventive </t>
+        </is>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59" t="inlineStr">
+        <is>
+          <t xml:space="preserve">VEDA - Dearator </t>
+        </is>
+      </c>
+      <c r="B59" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Remove dissolved oxygen from process water to prevent downstream corrosion </t>
+        </is>
+      </c>
+      <c r="C59" t="inlineStr">
+        <is>
+          <t>Outlet Nozzle Failure *</t>
+        </is>
+      </c>
+      <c r="D59" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Allow deaerated water to exit column to downstream equipment </t>
+        </is>
+      </c>
+      <c r="E59" t="inlineStr">
+        <is>
+          <t xml:space="preserve">NOI - Noise </t>
+        </is>
+      </c>
+      <c r="F59" t="inlineStr">
+        <is>
+          <t xml:space="preserve">5.2 Contamination </t>
+        </is>
+      </c>
+      <c r="G59" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Partial blockage creates cavitation noise at pump suction </t>
+        </is>
+      </c>
+      <c r="H59" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Outlet line checked for abnormal noise during operation? [Y/N] </t>
+        </is>
+      </c>
+      <c r="I59" t="inlineStr">
+        <is>
+          <t xml:space="preserve">TBD </t>
+        </is>
+      </c>
+      <c r="J59" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Predictive </t>
+        </is>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60" t="inlineStr">
+        <is>
+          <t xml:space="preserve">VEDA - Dearator </t>
+        </is>
+      </c>
+      <c r="B60" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Remove dissolved oxygen from process water to prevent downstream corrosion </t>
+        </is>
+      </c>
+      <c r="C60" t="inlineStr">
+        <is>
+          <t>Vapor/Vent Nozzle Failure (*) *</t>
+        </is>
+      </c>
+      <c r="D60" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Allow extracted gases (oxygen, CO2) to exit column </t>
+        </is>
+      </c>
+      <c r="E60" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ELP - External leakage - process medium </t>
+        </is>
+      </c>
+      <c r="F60" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2.2 Corrosion </t>
+        </is>
+      </c>
+      <c r="G60" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Corrosion of vent nozzle causes gas leakage </t>
+        </is>
+      </c>
+      <c r="H60" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Vent nozzle thickness verified by UT? [Y/N] </t>
+        </is>
+      </c>
+      <c r="I60" t="inlineStr">
+        <is>
+          <t xml:space="preserve">TBD </t>
+        </is>
+      </c>
+      <c r="J60" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Predictive </t>
+        </is>
+      </c>
+    </row>
+    <row r="61">
+      <c r="A61" t="inlineStr">
+        <is>
+          <t xml:space="preserve">VEDA - Dearator </t>
+        </is>
+      </c>
+      <c r="B61" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Remove dissolved oxygen from process water to prevent downstream corrosion </t>
+        </is>
+      </c>
+      <c r="C61" t="inlineStr">
+        <is>
+          <t>Vapor/Vent Nozzle Failure (*) *</t>
+        </is>
+      </c>
+      <c r="D61" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Allow extracted gases (oxygen, CO2) to exit column </t>
+        </is>
+      </c>
+      <c r="E61" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ELP - External leakage - process medium </t>
+        </is>
+      </c>
+      <c r="F61" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2.6 Fatigue </t>
+        </is>
+      </c>
+      <c r="G61" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Vibration in vent piping causes fatigue cracking at nozzle weld </t>
+        </is>
+      </c>
+      <c r="H61" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Vent piping supports condition checked? [Y/N] </t>
+        </is>
+      </c>
+      <c r="I61" t="inlineStr">
+        <is>
+          <t xml:space="preserve">TBD </t>
+        </is>
+      </c>
+      <c r="J61" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Preventive </t>
+        </is>
+      </c>
+    </row>
+    <row r="62">
+      <c r="A62" t="inlineStr">
+        <is>
+          <t xml:space="preserve">VEDA - Dearator </t>
+        </is>
+      </c>
+      <c r="B62" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Remove dissolved oxygen from process water to prevent downstream corrosion </t>
+        </is>
+      </c>
+      <c r="C62" t="inlineStr">
+        <is>
+          <t>Vapor/Vent Nozzle Failure (*) *</t>
+        </is>
+      </c>
+      <c r="D62" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Allow extracted gases (oxygen, CO2) to exit column </t>
+        </is>
+      </c>
+      <c r="E62" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ELP - External leakage - process medium </t>
+        </is>
+      </c>
+      <c r="F62" t="inlineStr">
+        <is>
+          <t xml:space="preserve">5.3 Miscellaneous external influences </t>
+        </is>
+      </c>
+      <c r="G62" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Mechanical impact damages vent nozzle or flange </t>
+        </is>
+      </c>
+      <c r="H62" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Vent nozzle free from visible damage? [Y/N] </t>
+        </is>
+      </c>
+      <c r="I62" t="inlineStr">
+        <is>
+          <t xml:space="preserve">TBD </t>
+        </is>
+      </c>
+      <c r="J62" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Preventive </t>
+        </is>
+      </c>
+    </row>
+    <row r="63">
+      <c r="A63" t="inlineStr">
+        <is>
+          <t xml:space="preserve">VEDA - Dearator </t>
+        </is>
+      </c>
+      <c r="B63" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Remove dissolved oxygen from process water to prevent downstream corrosion </t>
+        </is>
+      </c>
+      <c r="C63" t="inlineStr">
+        <is>
+          <t>Vapor/Vent Nozzle Failure (*) *</t>
+        </is>
+      </c>
+      <c r="D63" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Allow extracted gases (oxygen, CO2) to exit column </t>
+        </is>
+      </c>
+      <c r="E63" t="inlineStr">
+        <is>
+          <t xml:space="preserve">PLU - Plugged/choked </t>
+        </is>
+      </c>
+      <c r="F63" t="inlineStr">
+        <is>
+          <t xml:space="preserve">5.2 Contamination </t>
+        </is>
+      </c>
+      <c r="G63" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Debris or scaling inside vent nozzle restricts gas flow </t>
+        </is>
+      </c>
+      <c r="H63" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Vent system inspected for blockages during maintenance? [Y/N] </t>
+        </is>
+      </c>
+      <c r="I63" t="inlineStr">
+        <is>
+          <t xml:space="preserve">TBD </t>
+        </is>
+      </c>
+      <c r="J63" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Preventive </t>
+        </is>
+      </c>
+    </row>
+    <row r="64">
+      <c r="A64" t="inlineStr">
+        <is>
+          <t xml:space="preserve">VEDA - Dearator </t>
+        </is>
+      </c>
+      <c r="B64" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Remove dissolved oxygen from process water to prevent downstream corrosion </t>
+        </is>
+      </c>
+      <c r="C64" t="inlineStr">
+        <is>
+          <t>Vapor/Vent Nozzle Failure (*) *</t>
+        </is>
+      </c>
+      <c r="D64" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Allow extracted gases (oxygen, CO2) to exit column </t>
+        </is>
+      </c>
+      <c r="E64" t="inlineStr">
+        <is>
+          <t xml:space="preserve">PLU - Plugged/choked </t>
+        </is>
+      </c>
+      <c r="F64" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2.2 Corrosion </t>
+        </is>
+      </c>
+      <c r="G64" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Corrosion debris accumulation blocks gas passage </t>
+        </is>
+      </c>
+      <c r="H64" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Vent nozzle internal condition inspected? [Y/N] </t>
+        </is>
+      </c>
+      <c r="I64" t="inlineStr">
+        <is>
+          <t xml:space="preserve">TBD </t>
+        </is>
+      </c>
+      <c r="J64" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Preventive </t>
+        </is>
+      </c>
+    </row>
+    <row r="65">
+      <c r="A65" t="inlineStr">
+        <is>
+          <t xml:space="preserve">VEDA - Dearator </t>
+        </is>
+      </c>
+      <c r="B65" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Remove dissolved oxygen from process water to prevent downstream corrosion </t>
+        </is>
+      </c>
+      <c r="C65" t="inlineStr">
+        <is>
+          <t>Vapor/Vent Nozzle Failure (*) *</t>
+        </is>
+      </c>
+      <c r="D65" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Allow extracted gases (oxygen, CO2) to exit column </t>
+        </is>
+      </c>
+      <c r="E65" t="inlineStr">
+        <is>
+          <t xml:space="preserve">PDE - Parameter deviation </t>
+        </is>
+      </c>
+      <c r="F65" t="inlineStr">
+        <is>
+          <t xml:space="preserve">5.2 Contamination </t>
+        </is>
+      </c>
+      <c r="G65" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Restricted vent flow causes column top pressure deviation </t>
+        </is>
+      </c>
+      <c r="H65" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Column top pressure compared to design target? [Y/N] </t>
+        </is>
+      </c>
+      <c r="I65" t="inlineStr">
+        <is>
+          <t xml:space="preserve">TBD </t>
+        </is>
+      </c>
+      <c r="J65" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Predictive </t>
+        </is>
+      </c>
+    </row>
+    <row r="66">
+      <c r="A66" t="inlineStr">
+        <is>
+          <t xml:space="preserve">VEDA - Dearator </t>
+        </is>
+      </c>
+      <c r="B66" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Remove dissolved oxygen from process water to prevent downstream corrosion </t>
+        </is>
+      </c>
+      <c r="C66" t="inlineStr">
+        <is>
+          <t>Vapor/Vent Nozzle Failure (*) *</t>
+        </is>
+      </c>
+      <c r="D66" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Allow extracted gases (oxygen, CO2) to exit column </t>
+        </is>
+      </c>
+      <c r="E66" t="inlineStr">
+        <is>
+          <t xml:space="preserve">PDE - Parameter deviation </t>
+        </is>
+      </c>
+      <c r="F66" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2.2 Corrosion </t>
+        </is>
+      </c>
+      <c r="G66" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Corrosion changes nozzle internal flow area affecting vent capacity </t>
+        </is>
+      </c>
+      <c r="H66" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Vent nozzle internal diameter verified? [Y/N] </t>
+        </is>
+      </c>
+      <c r="I66" t="inlineStr">
+        <is>
+          <t xml:space="preserve">TBD </t>
+        </is>
+      </c>
+      <c r="J66" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Preventive </t>
+        </is>
+      </c>
+    </row>
+    <row r="67">
+      <c r="A67" t="inlineStr">
+        <is>
+          <t xml:space="preserve">VEDA - Dearator </t>
+        </is>
+      </c>
+      <c r="B67" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Remove dissolved oxygen from process water to prevent downstream corrosion </t>
+        </is>
+      </c>
+      <c r="C67" t="inlineStr">
+        <is>
+          <t>Vapor/Vent Nozzle Failure (*) *</t>
+        </is>
+      </c>
+      <c r="D67" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Allow extracted gases (oxygen, CO2) to exit column </t>
+        </is>
+      </c>
+      <c r="E67" t="inlineStr">
+        <is>
+          <t xml:space="preserve">STD - Structural deficiency </t>
+        </is>
+      </c>
+      <c r="F67" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2.2 Corrosion </t>
+        </is>
+      </c>
+      <c r="G67" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Corrosion thinning reduces structural integrity </t>
+        </is>
+      </c>
+      <c r="H67" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Vent nozzle minimum thickness verified? [Y/N] </t>
+        </is>
+      </c>
+      <c r="I67" t="inlineStr">
+        <is>
+          <t xml:space="preserve">TBD </t>
+        </is>
+      </c>
+      <c r="J67" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Predictive </t>
+        </is>
+      </c>
+    </row>
+    <row r="68">
+      <c r="A68" t="inlineStr">
+        <is>
+          <t xml:space="preserve">VEDA - Dearator </t>
+        </is>
+      </c>
+      <c r="B68" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Remove dissolved oxygen from process water to prevent downstream corrosion </t>
+        </is>
+      </c>
+      <c r="C68" t="inlineStr">
+        <is>
+          <t>Vapor/Vent Nozzle Failure (*) *</t>
+        </is>
+      </c>
+      <c r="D68" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Allow extracted gases (oxygen, CO2) to exit column </t>
+        </is>
+      </c>
+      <c r="E68" t="inlineStr">
+        <is>
+          <t xml:space="preserve">STD - Structural deficiency </t>
+        </is>
+      </c>
+      <c r="F68" t="inlineStr">
+        <is>
+          <t xml:space="preserve">5.3 Miscellaneous external influences </t>
+        </is>
+      </c>
+      <c r="G68" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Mechanical damage to vent piping or nozzle </t>
+        </is>
+      </c>
+      <c r="H68" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Vent nozzle and piping free from damage? [Y/N] </t>
+        </is>
+      </c>
+      <c r="I68" t="inlineStr">
+        <is>
+          <t xml:space="preserve">TBD </t>
+        </is>
+      </c>
+      <c r="J68" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Preventive </t>
+        </is>
+      </c>
+    </row>
+    <row r="69">
+      <c r="A69" t="inlineStr">
+        <is>
+          <t xml:space="preserve">VEDA - Dearator </t>
+        </is>
+      </c>
+      <c r="B69" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Remove dissolved oxygen from process water to prevent downstream corrosion </t>
+        </is>
+      </c>
+      <c r="C69" t="inlineStr">
+        <is>
+          <t>Vapor/Vent Nozzle Failure (*) *</t>
+        </is>
+      </c>
+      <c r="D69" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Allow extracted gases (oxygen, CO2) to exit column </t>
+        </is>
+      </c>
+      <c r="E69" t="inlineStr">
+        <is>
+          <t xml:space="preserve">VIB - Vibration </t>
+        </is>
+      </c>
+      <c r="F69" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2.6 Fatigue </t>
+        </is>
+      </c>
+      <c r="G69" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gas flow-induced vibration causes structural fatigue </t>
+        </is>
+      </c>
+      <c r="H69" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Vent nozzle vibration levels monitored? [Y/N] </t>
+        </is>
+      </c>
+      <c r="I69" t="inlineStr">
+        <is>
+          <t xml:space="preserve">TBD </t>
+        </is>
+      </c>
+      <c r="J69" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Predictive </t>
+        </is>
+      </c>
+    </row>
+    <row r="70">
+      <c r="A70" t="inlineStr">
+        <is>
+          <t xml:space="preserve">VEDA - Dearator </t>
+        </is>
+      </c>
+      <c r="B70" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Remove dissolved oxygen from process water to prevent downstream corrosion </t>
+        </is>
+      </c>
+      <c r="C70" t="inlineStr">
+        <is>
+          <t>Vapor/Vent Nozzle Failure (*) *</t>
+        </is>
+      </c>
+      <c r="D70" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Allow extracted gases (oxygen, CO2) to exit column </t>
+        </is>
+      </c>
+      <c r="E70" t="inlineStr">
+        <is>
+          <t xml:space="preserve">VIB - Vibration </t>
+        </is>
+      </c>
+      <c r="F70" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1.5 Looseness </t>
+        </is>
+      </c>
+      <c r="G70" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Loose vent piping support allows nozzle vibration </t>
+        </is>
+      </c>
+      <c r="H70" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Vent piping supports verified tight? [Y/N] </t>
+        </is>
+      </c>
+      <c r="I70" t="inlineStr">
+        <is>
+          <t xml:space="preserve">TBD </t>
+        </is>
+      </c>
+      <c r="J70" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Preventive </t>
+        </is>
+      </c>
+    </row>
+    <row r="71">
+      <c r="A71" t="inlineStr">
+        <is>
+          <t xml:space="preserve">VEDA - Dearator </t>
+        </is>
+      </c>
+      <c r="B71" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Remove dissolved oxygen from process water to prevent downstream corrosion </t>
+        </is>
+      </c>
+      <c r="C71" t="inlineStr">
+        <is>
+          <t>Vapor/Vent Nozzle Failure (*) *</t>
+        </is>
+      </c>
+      <c r="D71" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Allow extracted gases (oxygen, CO2) to exit column </t>
+        </is>
+      </c>
+      <c r="E71" t="inlineStr">
+        <is>
+          <t xml:space="preserve">NOI - Noise </t>
+        </is>
+      </c>
+      <c r="F71" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2.3 Erosion </t>
+        </is>
+      </c>
+      <c r="G71" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Erosion of vent nozzle creates turbulence causing gas flow noise </t>
+        </is>
+      </c>
+      <c r="H71" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Vent nozzle internal inspected for erosion? [Y/N] </t>
+        </is>
+      </c>
+      <c r="I71" t="inlineStr">
+        <is>
+          <t xml:space="preserve">TBD </t>
+        </is>
+      </c>
+      <c r="J71" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Preventive </t>
+        </is>
+      </c>
+    </row>
+    <row r="72">
+      <c r="A72" t="inlineStr">
+        <is>
+          <t xml:space="preserve">VEDA - Dearator </t>
+        </is>
+      </c>
+      <c r="B72" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Remove dissolved oxygen from process water to prevent downstream corrosion </t>
+        </is>
+      </c>
+      <c r="C72" t="inlineStr">
+        <is>
+          <t>Vapor/Vent Nozzle Failure (*) *</t>
+        </is>
+      </c>
+      <c r="D72" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Allow extracted gases (oxygen, CO2) to exit column </t>
+        </is>
+      </c>
+      <c r="E72" t="inlineStr">
+        <is>
+          <t xml:space="preserve">NOI - Noise </t>
+        </is>
+      </c>
+      <c r="F72" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2.6 Fatigue </t>
+        </is>
+      </c>
+      <c r="G72" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gas leak through developing crack creates hissing sound </t>
+        </is>
+      </c>
+      <c r="H72" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Vent line checked for audible gas leaks? [Y/N] </t>
+        </is>
+      </c>
+      <c r="I72" t="inlineStr">
+        <is>
+          <t xml:space="preserve">TBD </t>
+        </is>
+      </c>
+      <c r="J72" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Preventive </t>
+        </is>
+      </c>
+    </row>
+    <row r="73">
+      <c r="A73" t="inlineStr">
+        <is>
+          <t xml:space="preserve">VEDA - Dearator </t>
+        </is>
+      </c>
+      <c r="B73" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Remove dissolved oxygen from process water to prevent downstream corrosion </t>
+        </is>
+      </c>
+      <c r="C73" t="inlineStr">
+        <is>
+          <t>Drain Nozzle Failure (*) *</t>
+        </is>
+      </c>
+      <c r="D73" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Allow removal of accumulated sediment and water during maintenance </t>
+        </is>
+      </c>
+      <c r="E73" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ELP - External leakage - process medium </t>
+        </is>
+      </c>
+      <c r="F73" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2.2 Corrosion </t>
+        </is>
+      </c>
+      <c r="G73" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Corrosion of drain nozzle causes water leak </t>
+        </is>
+      </c>
+      <c r="H73" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Drain nozzle thickness verified by UT? [Y/N] </t>
+        </is>
+      </c>
+      <c r="I73" t="inlineStr">
+        <is>
+          <t xml:space="preserve">TBD </t>
+        </is>
+      </c>
+      <c r="J73" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Predictive </t>
+        </is>
+      </c>
+    </row>
+    <row r="74">
+      <c r="A74" t="inlineStr">
+        <is>
+          <t xml:space="preserve">VEDA - Dearator </t>
+        </is>
+      </c>
+      <c r="B74" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Remove dissolved oxygen from process water to prevent downstream corrosion </t>
+        </is>
+      </c>
+      <c r="C74" t="inlineStr">
+        <is>
+          <t>Drain Nozzle Failure (*) *</t>
+        </is>
+      </c>
+      <c r="D74" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Allow removal of accumulated sediment and water during maintenance </t>
+        </is>
+      </c>
+      <c r="E74" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ELP - External leakage - process medium </t>
+        </is>
+      </c>
+      <c r="F74" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2.3 Erosion </t>
+        </is>
+      </c>
+      <c r="G74" t="inlineStr">
+        <is>
+          <t xml:space="preserve">High-velocity drain flow during blowdown erodes nozzle </t>
+        </is>
+      </c>
+      <c r="H74" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Drain nozzle wall thickness measured? [Y/N] </t>
+        </is>
+      </c>
+      <c r="I74" t="inlineStr">
+        <is>
+          <t xml:space="preserve">TBD </t>
+        </is>
+      </c>
+      <c r="J74" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Predictive </t>
+        </is>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75" t="inlineStr">
+        <is>
+          <t xml:space="preserve">VEDA - Dearator </t>
+        </is>
+      </c>
+      <c r="B75" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Remove dissolved oxygen from process water to prevent downstream corrosion </t>
+        </is>
+      </c>
+      <c r="C75" t="inlineStr">
+        <is>
+          <t>Drain Nozzle Failure (*) *</t>
+        </is>
+      </c>
+      <c r="D75" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Allow removal of accumulated sediment and water during maintenance </t>
+        </is>
+      </c>
+      <c r="E75" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ELP - External leakage - process medium </t>
+        </is>
+      </c>
+      <c r="F75" t="inlineStr">
+        <is>
+          <t xml:space="preserve">5.3 Miscellaneous external influences </t>
+        </is>
+      </c>
+      <c r="G75" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Mechanical impact during maintenance damages drain nozzle </t>
+        </is>
+      </c>
+      <c r="H75" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Drain nozzle free from mechanical damage? [Y/N] </t>
+        </is>
+      </c>
+      <c r="I75" t="inlineStr">
+        <is>
+          <t xml:space="preserve">TBD </t>
+        </is>
+      </c>
+      <c r="J75" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Preventive </t>
+        </is>
+      </c>
+    </row>
+    <row r="76">
+      <c r="A76" t="inlineStr">
+        <is>
+          <t xml:space="preserve">VEDA - Dearator </t>
+        </is>
+      </c>
+      <c r="B76" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Remove dissolved oxygen from process water to prevent downstream corrosion </t>
+        </is>
+      </c>
+      <c r="C76" t="inlineStr">
+        <is>
+          <t>Drain Nozzle Failure (*) *</t>
+        </is>
+      </c>
+      <c r="D76" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Allow removal of accumulated sediment and water during maintenance </t>
+        </is>
+      </c>
+      <c r="E76" t="inlineStr">
+        <is>
+          <t xml:space="preserve">PLU - Plugged/choked </t>
+        </is>
+      </c>
+      <c r="F76" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2.2 Corrosion </t>
+        </is>
+      </c>
+      <c r="G76" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Corrosion debris and scale block drain preventing flow </t>
+        </is>
+      </c>
+      <c r="H76" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Drain functionality tested during column shutdown? [Y/N] </t>
+        </is>
+      </c>
+      <c r="I76" t="inlineStr">
+        <is>
+          <t xml:space="preserve">TBD </t>
+        </is>
+      </c>
+      <c r="J76" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Failure-Finding </t>
+        </is>
+      </c>
+    </row>
+    <row r="77">
+      <c r="A77" t="inlineStr">
+        <is>
+          <t xml:space="preserve">VEDA - Dearator </t>
+        </is>
+      </c>
+      <c r="B77" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Remove dissolved oxygen from process water to prevent downstream corrosion </t>
+        </is>
+      </c>
+      <c r="C77" t="inlineStr">
+        <is>
+          <t>Drain Nozzle Failure (*) *</t>
+        </is>
+      </c>
+      <c r="D77" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Allow removal of accumulated sediment and water during maintenance </t>
+        </is>
+      </c>
+      <c r="E77" t="inlineStr">
+        <is>
+          <t xml:space="preserve">PLU - Plugged/choked </t>
+        </is>
+      </c>
+      <c r="F77" t="inlineStr">
+        <is>
+          <t xml:space="preserve">5.2 Contamination </t>
+        </is>
+      </c>
+      <c r="G77" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Sediment accumulation inside drain restricts flow </t>
+        </is>
+      </c>
+      <c r="H77" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Drain nozzle cleaned and verified clear? [Y/N] </t>
+        </is>
+      </c>
+      <c r="I77" t="inlineStr">
+        <is>
+          <t xml:space="preserve">TBD </t>
+        </is>
+      </c>
+      <c r="J77" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Preventive </t>
+        </is>
+      </c>
+    </row>
+    <row r="78">
+      <c r="A78" t="inlineStr">
+        <is>
+          <t xml:space="preserve">VEDA - Dearator </t>
+        </is>
+      </c>
+      <c r="B78" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Remove dissolved oxygen from process water to prevent downstream corrosion </t>
+        </is>
+      </c>
+      <c r="C78" t="inlineStr">
+        <is>
+          <t>Drain Nozzle Failure (*) *</t>
+        </is>
+      </c>
+      <c r="D78" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Allow removal of accumulated sediment and water during maintenance </t>
+        </is>
+      </c>
+      <c r="E78" t="inlineStr">
+        <is>
+          <t xml:space="preserve">STD - Structural deficiency </t>
+        </is>
+      </c>
+      <c r="F78" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2.2 Corrosion </t>
+        </is>
+      </c>
+      <c r="G78" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Wall thinning from localized low-point corrosion </t>
+        </is>
+      </c>
+      <c r="H78" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Drain nozzle remaining thickness verified? [Y/N] </t>
+        </is>
+      </c>
+      <c r="I78" t="inlineStr">
+        <is>
+          <t xml:space="preserve">TBD </t>
+        </is>
+      </c>
+      <c r="J78" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Predictive </t>
+        </is>
+      </c>
+    </row>
+    <row r="79">
+      <c r="A79" t="inlineStr">
+        <is>
+          <t xml:space="preserve">VEDA - Dearator </t>
+        </is>
+      </c>
+      <c r="B79" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Remove dissolved oxygen from process water to prevent downstream corrosion </t>
+        </is>
+      </c>
+      <c r="C79" t="inlineStr">
+        <is>
+          <t>Drain Nozzle Failure (*) *</t>
+        </is>
+      </c>
+      <c r="D79" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Allow removal of accumulated sediment and water during maintenance </t>
+        </is>
+      </c>
+      <c r="E79" t="inlineStr">
+        <is>
+          <t xml:space="preserve">STD - Structural deficiency </t>
+        </is>
+      </c>
+      <c r="F79" t="inlineStr">
+        <is>
+          <t xml:space="preserve">5.3 Miscellaneous external influences </t>
+        </is>
+      </c>
+      <c r="G79" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Impact during maintenance damages drain nozzle structure </t>
+        </is>
+      </c>
+      <c r="H79" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Drain nozzle free from visible deformation? [Y/N] </t>
+        </is>
+      </c>
+      <c r="I79" t="inlineStr">
+        <is>
+          <t xml:space="preserve">TBD </t>
+        </is>
+      </c>
+      <c r="J79" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Preventive </t>
+        </is>
+      </c>
+    </row>
+    <row r="80">
+      <c r="A80" t="inlineStr">
+        <is>
+          <t xml:space="preserve">VEDA - Dearator </t>
+        </is>
+      </c>
+      <c r="B80" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Remove dissolved oxygen from process water to prevent downstream corrosion </t>
+        </is>
+      </c>
+      <c r="C80" t="inlineStr">
+        <is>
+          <t>Drain Nozzle Failure (*) *</t>
+        </is>
+      </c>
+      <c r="D80" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Allow removal of accumulated sediment and water during maintenance </t>
+        </is>
+      </c>
+      <c r="E80" t="inlineStr">
+        <is>
+          <t xml:space="preserve">PDE - Parameter deviation </t>
+        </is>
+      </c>
+      <c r="F80" t="inlineStr">
+        <is>
+          <t xml:space="preserve">5.2 Contamination </t>
+        </is>
+      </c>
+      <c r="G80" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Partially blocked drain prevents effective sludge removal </t>
+        </is>
+      </c>
+      <c r="H80" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Bottom drain flushed and effluent quality checked? [Y/N] </t>
+        </is>
+      </c>
+      <c r="I80" t="inlineStr">
+        <is>
+          <t xml:space="preserve">TBD </t>
+        </is>
+      </c>
+      <c r="J80" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Preventive </t>
+        </is>
+      </c>
+    </row>
+    <row r="81">
+      <c r="A81" t="inlineStr">
+        <is>
+          <t xml:space="preserve">VEDA - Dearator </t>
+        </is>
+      </c>
+      <c r="B81" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Remove dissolved oxygen from process water to prevent downstream corrosion </t>
+        </is>
+      </c>
+      <c r="C81" t="inlineStr">
+        <is>
+          <t>Drain Nozzle Failure (*) *</t>
+        </is>
+      </c>
+      <c r="D81" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Allow removal of accumulated sediment and water during maintenance </t>
+        </is>
+      </c>
+      <c r="E81" t="inlineStr">
+        <is>
+          <t xml:space="preserve">PDE - Parameter deviation </t>
+        </is>
+      </c>
+      <c r="F81" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2.2 Corrosion </t>
+        </is>
+      </c>
+      <c r="G81" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Corrosion restricts internal diameter affecting drain flow capacity </t>
+        </is>
+      </c>
+      <c r="H81" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Drain nozzle internal condition inspected? [Y/N] </t>
+        </is>
+      </c>
+      <c r="I81" t="inlineStr">
+        <is>
+          <t xml:space="preserve">TBD </t>
+        </is>
+      </c>
+      <c r="J81" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Preventive </t>
+        </is>
+      </c>
+    </row>
+    <row r="82">
+      <c r="A82" t="inlineStr">
+        <is>
+          <t xml:space="preserve">VEDA - Dearator </t>
+        </is>
+      </c>
+      <c r="B82" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Remove dissolved oxygen from process water to prevent downstream corrosion </t>
+        </is>
+      </c>
+      <c r="C82" t="inlineStr">
+        <is>
+          <t>Drain Nozzle Failure (*) *</t>
+        </is>
+      </c>
+      <c r="D82" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Allow removal of accumulated sediment and water during maintenance </t>
+        </is>
+      </c>
+      <c r="E82" t="inlineStr">
+        <is>
+          <t xml:space="preserve">SBU - Sludge build-up </t>
+        </is>
+      </c>
+      <c r="F82" t="inlineStr">
+        <is>
+          <t xml:space="preserve">5.2 Contamination </t>
+        </is>
+      </c>
+      <c r="G82" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Sediment accumulation at sump restricts drain flow </t>
+        </is>
+      </c>
+      <c r="H82" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Column bottom sump sludge level checked? [Y/N] </t>
+        </is>
+      </c>
+      <c r="I82" t="inlineStr">
+        <is>
+          <t xml:space="preserve">TBD </t>
+        </is>
+      </c>
+      <c r="J82" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Preventive </t>
+        </is>
+      </c>
+    </row>
+    <row r="83">
+      <c r="A83" t="inlineStr">
+        <is>
+          <t xml:space="preserve">VEDA - Dearator </t>
+        </is>
+      </c>
+      <c r="B83" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Remove dissolved oxygen from process water to prevent downstream corrosion </t>
+        </is>
+      </c>
+      <c r="C83" t="inlineStr">
+        <is>
+          <t>Drain Nozzle Failure (*) *</t>
+        </is>
+      </c>
+      <c r="D83" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Allow removal of accumulated sediment and water during maintenance </t>
+        </is>
+      </c>
+      <c r="E83" t="inlineStr">
+        <is>
+          <t xml:space="preserve">SBU - Sludge build-up </t>
+        </is>
+      </c>
+      <c r="F83" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2.2 Corrosion </t>
+        </is>
+      </c>
+      <c r="G83" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Corrosion by-products accelerate sludge accumulation </t>
+        </is>
+      </c>
+      <c r="H83" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Bottom sediment sample analyzed? [Y/N] </t>
+        </is>
+      </c>
+      <c r="I83" t="inlineStr">
+        <is>
+          <t xml:space="preserve">TBD </t>
+        </is>
+      </c>
+      <c r="J83" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Predictive </t>
+        </is>
+      </c>
+    </row>
+    <row r="84">
+      <c r="A84" t="inlineStr">
+        <is>
+          <t xml:space="preserve">VEDA - Dearator </t>
+        </is>
+      </c>
+      <c r="B84" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Remove dissolved oxygen from process water to prevent downstream corrosion </t>
+        </is>
+      </c>
+      <c r="C84" t="inlineStr">
+        <is>
+          <t>Manhole Failure (*) *</t>
+        </is>
+      </c>
+      <c r="D84" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Provide personnel access for inspection and maintenance </t>
+        </is>
+      </c>
+      <c r="E84" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ELP - External leakage - process medium </t>
+        </is>
+      </c>
+      <c r="F84" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2.2 Corrosion </t>
+        </is>
+      </c>
+      <c r="G84" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Corrosion on seating surface prevents leak-tight seal </t>
+        </is>
+      </c>
+      <c r="H84" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Manhole gasket and seating surface inspected? [Y/N] </t>
+        </is>
+      </c>
+      <c r="I84" t="inlineStr">
+        <is>
+          <t xml:space="preserve">TBD </t>
+        </is>
+      </c>
+      <c r="J84" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Preventive </t>
+        </is>
+      </c>
+    </row>
+    <row r="85">
+      <c r="A85" t="inlineStr">
+        <is>
+          <t xml:space="preserve">VEDA - Dearator </t>
+        </is>
+      </c>
+      <c r="B85" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Remove dissolved oxygen from process water to prevent downstream corrosion </t>
+        </is>
+      </c>
+      <c r="C85" t="inlineStr">
+        <is>
+          <t>Manhole Failure (*) *</t>
+        </is>
+      </c>
+      <c r="D85" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Provide personnel access for inspection and maintenance </t>
+        </is>
+      </c>
+      <c r="E85" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ELP - External leakage - process medium </t>
+        </is>
+      </c>
+      <c r="F85" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1.4 Deformation </t>
+        </is>
+      </c>
+      <c r="G85" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gasket failure or bolt over-torquing causes leak path </t>
+        </is>
+      </c>
+      <c r="H85" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Manhole bolts tightened to specified torque? [Y/N] </t>
+        </is>
+      </c>
+      <c r="I85" t="inlineStr">
+        <is>
+          <t xml:space="preserve">TBD </t>
+        </is>
+      </c>
+      <c r="J85" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Preventive </t>
+        </is>
+      </c>
+    </row>
+    <row r="86">
+      <c r="A86" t="inlineStr">
+        <is>
+          <t xml:space="preserve">VEDA - Dearator </t>
+        </is>
+      </c>
+      <c r="B86" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Remove dissolved oxygen from process water to prevent downstream corrosion </t>
+        </is>
+      </c>
+      <c r="C86" t="inlineStr">
+        <is>
+          <t>Manhole Failure (*) *</t>
+        </is>
+      </c>
+      <c r="D86" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Provide personnel access for inspection and maintenance </t>
+        </is>
+      </c>
+      <c r="E86" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ELP - External leakage - process medium </t>
+        </is>
+      </c>
+      <c r="F86" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2.6 Fatigue </t>
+        </is>
+      </c>
+      <c r="G86" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Thermal cycling causes fatigue crack at manhole joint </t>
+        </is>
+      </c>
+      <c r="H86" t="inlineStr">
+        <is>
+          <t xml:space="preserve">NDT of manhole weld performed? [Y/N] </t>
+        </is>
+      </c>
+      <c r="I86" t="inlineStr">
+        <is>
+          <t xml:space="preserve">TBD </t>
+        </is>
+      </c>
+      <c r="J86" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Predictive </t>
+        </is>
+      </c>
+    </row>
+    <row r="87">
+      <c r="A87" t="inlineStr">
+        <is>
+          <t xml:space="preserve">VEDA - Dearator </t>
+        </is>
+      </c>
+      <c r="B87" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Remove dissolved oxygen from process water to prevent downstream corrosion </t>
+        </is>
+      </c>
+      <c r="C87" t="inlineStr">
+        <is>
+          <t>Manhole Failure (*) *</t>
+        </is>
+      </c>
+      <c r="D87" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Provide personnel access for inspection and maintenance </t>
+        </is>
+      </c>
+      <c r="E87" t="inlineStr">
+        <is>
+          <t xml:space="preserve">STD - Structural deficiency </t>
+        </is>
+      </c>
+      <c r="F87" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2.2 Corrosion </t>
+        </is>
+      </c>
+      <c r="G87" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Corrosion of flange or studs reduces fastener integrity </t>
+        </is>
+      </c>
+      <c r="H87" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Manhole studs/bolts condition and dimension verified? [Y/N] </t>
+        </is>
+      </c>
+      <c r="I87" t="inlineStr">
+        <is>
+          <t xml:space="preserve">TBD </t>
+        </is>
+      </c>
+      <c r="J87" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Preventive </t>
+        </is>
+      </c>
+    </row>
+    <row r="88">
+      <c r="A88" t="inlineStr">
+        <is>
+          <t xml:space="preserve">VEDA - Dearator </t>
+        </is>
+      </c>
+      <c r="B88" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Remove dissolved oxygen from process water to prevent downstream corrosion </t>
+        </is>
+      </c>
+      <c r="C88" t="inlineStr">
+        <is>
+          <t>Manhole Failure (*) *</t>
+        </is>
+      </c>
+      <c r="D88" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Provide personnel access for inspection and maintenance </t>
+        </is>
+      </c>
+      <c r="E88" t="inlineStr">
+        <is>
+          <t xml:space="preserve">STD - Structural deficiency </t>
+        </is>
+      </c>
+      <c r="F88" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2.6 Fatigue </t>
+        </is>
+      </c>
+      <c r="G88" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Fatigue cracking at manhole-to-shell weld </t>
+        </is>
+      </c>
+      <c r="H88" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Manhole weld NDT performed within inspection interval? [Y/N] </t>
+        </is>
+      </c>
+      <c r="I88" t="inlineStr">
+        <is>
+          <t xml:space="preserve">TBD </t>
+        </is>
+      </c>
+      <c r="J88" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Predictive </t>
+        </is>
+      </c>
+    </row>
+    <row r="89">
+      <c r="A89" t="inlineStr">
+        <is>
+          <t xml:space="preserve">VEDA - Dearator </t>
+        </is>
+      </c>
+      <c r="B89" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Remove dissolved oxygen from process water to prevent downstream corrosion </t>
+        </is>
+      </c>
+      <c r="C89" t="inlineStr">
+        <is>
+          <t>Manhole Failure (*) *</t>
+        </is>
+      </c>
+      <c r="D89" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Provide personnel access for inspection and maintenance </t>
+        </is>
+      </c>
+      <c r="E89" t="inlineStr">
+        <is>
+          <t xml:space="preserve">STD - Structural deficiency </t>
+        </is>
+      </c>
+      <c r="F89" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1.4 Deformation </t>
+        </is>
+      </c>
+      <c r="G89" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Manhole flange warped from overtightening </t>
+        </is>
+      </c>
+      <c r="H89" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Manhole flange flatness verified? [Y/N] </t>
+        </is>
+      </c>
+      <c r="I89" t="inlineStr">
+        <is>
+          <t xml:space="preserve">TBD </t>
+        </is>
+      </c>
+      <c r="J89" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Preventive </t>
+        </is>
+      </c>
+    </row>
+    <row r="90">
+      <c r="A90" t="inlineStr">
+        <is>
+          <t xml:space="preserve">VEDA - Dearator </t>
+        </is>
+      </c>
+      <c r="B90" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Remove dissolved oxygen from process water to prevent downstream corrosion </t>
+        </is>
+      </c>
+      <c r="C90" t="inlineStr">
+        <is>
+          <t>Manhole Failure (*) *</t>
+        </is>
+      </c>
+      <c r="D90" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Provide personnel access for inspection and maintenance </t>
+        </is>
+      </c>
+      <c r="E90" t="inlineStr">
+        <is>
+          <t xml:space="preserve">PDE - Parameter deviation </t>
+        </is>
+      </c>
+      <c r="F90" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1.4 Deformation </t>
+        </is>
+      </c>
+      <c r="G90" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Warped cover prevents seal affecting column vacuum/pressure </t>
+        </is>
+      </c>
+      <c r="H90" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Manhole cover condition inspected and seal verified? [Y/N] </t>
+        </is>
+      </c>
+      <c r="I90" t="inlineStr">
+        <is>
+          <t xml:space="preserve">TBD </t>
+        </is>
+      </c>
+      <c r="J90" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Preventive </t>
+        </is>
+      </c>
+    </row>
+    <row r="91">
+      <c r="A91" t="inlineStr">
+        <is>
+          <t xml:space="preserve">VEDA - Dearator </t>
+        </is>
+      </c>
+      <c r="B91" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Remove dissolved oxygen from process water to prevent downstream corrosion </t>
+        </is>
+      </c>
+      <c r="C91" t="inlineStr">
+        <is>
+          <t>Manhole Failure (*) *</t>
+        </is>
+      </c>
+      <c r="D91" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Provide personnel access for inspection and maintenance </t>
+        </is>
+      </c>
+      <c r="E91" t="inlineStr">
+        <is>
+          <t xml:space="preserve">PDE - Parameter deviation </t>
+        </is>
+      </c>
+      <c r="F91" t="inlineStr">
+        <is>
+          <t xml:space="preserve">5.2 Contamination </t>
+        </is>
+      </c>
+      <c r="G91" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Debris on sealing surface prevents closure </t>
+        </is>
+      </c>
+      <c r="H91" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Manhole seating surface clean and free of debris? [Y/N] </t>
+        </is>
+      </c>
+      <c r="I91" t="inlineStr">
+        <is>
+          <t xml:space="preserve">TBD </t>
+        </is>
+      </c>
+      <c r="J91" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Preventive </t>
+        </is>
+      </c>
+    </row>
+    <row r="92">
+      <c r="A92" t="inlineStr">
+        <is>
+          <t xml:space="preserve">VEDA - Dearator </t>
+        </is>
+      </c>
+      <c r="B92" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Remove dissolved oxygen from process water to prevent downstream corrosion </t>
+        </is>
+      </c>
+      <c r="C92" t="inlineStr">
+        <is>
+          <t>Manhole Failure (*) *</t>
+        </is>
+      </c>
+      <c r="D92" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Provide personnel access for inspection and maintenance </t>
+        </is>
+      </c>
+      <c r="E92" t="inlineStr">
+        <is>
+          <t xml:space="preserve">VIB - Vibration </t>
+        </is>
+      </c>
+      <c r="F92" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1.5 Looseness </t>
+        </is>
+      </c>
+      <c r="G92" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Loose cover bolts cause vibration under pressure cycling </t>
+        </is>
+      </c>
+      <c r="H92" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Manhole cover bolts verified tight? [Y/N] </t>
+        </is>
+      </c>
+      <c r="I92" t="inlineStr">
+        <is>
+          <t xml:space="preserve">TBD </t>
+        </is>
+      </c>
+      <c r="J92" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Preventive </t>
+        </is>
+      </c>
+    </row>
+    <row r="93">
+      <c r="A93" t="inlineStr">
+        <is>
+          <t xml:space="preserve">VEDA - Dearator </t>
+        </is>
+      </c>
+      <c r="B93" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Remove dissolved oxygen from process water to prevent downstream corrosion </t>
+        </is>
+      </c>
+      <c r="C93" t="inlineStr">
+        <is>
+          <t>Manhole Failure (*) *</t>
+        </is>
+      </c>
+      <c r="D93" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Provide personnel access for inspection and maintenance </t>
+        </is>
+      </c>
+      <c r="E93" t="inlineStr">
+        <is>
+          <t xml:space="preserve">VIB - Vibration </t>
+        </is>
+      </c>
+      <c r="F93" t="inlineStr">
+        <is>
+          <t xml:space="preserve">5.3 Miscellaneous external influences </t>
+        </is>
+      </c>
+      <c r="G93" t="inlineStr">
+        <is>
+          <t xml:space="preserve">External vibration transmitted to manhole cover </t>
+        </is>
+      </c>
+      <c r="H93" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Manhole cover secured and locking feature engaged? [Y/N] </t>
+        </is>
+      </c>
+      <c r="I93" t="inlineStr">
+        <is>
+          <t xml:space="preserve">TBD </t>
+        </is>
+      </c>
+      <c r="J93" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Preventive </t>
+        </is>
+      </c>
+    </row>
+    <row r="94">
+      <c r="A94" t="inlineStr">
+        <is>
+          <t xml:space="preserve">VEDA - Dearator </t>
+        </is>
+      </c>
+      <c r="B94" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Remove dissolved oxygen from process water to prevent downstream corrosion </t>
+        </is>
+      </c>
+      <c r="C94" t="inlineStr">
+        <is>
+          <t>Manhole Failure (*) *</t>
+        </is>
+      </c>
+      <c r="D94" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Provide personnel access for inspection and maintenance </t>
+        </is>
+      </c>
+      <c r="E94" t="inlineStr">
+        <is>
+          <t xml:space="preserve">NOI - Noise </t>
+        </is>
+      </c>
+      <c r="F94" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1.5 Looseness </t>
+        </is>
+      </c>
+      <c r="G94" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Loose hardware creates rattling noise under vibration </t>
+        </is>
+      </c>
+      <c r="H94" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Manhole hardware condition and tightness verified? [Y/N] </t>
+        </is>
+      </c>
+      <c r="I94" t="inlineStr">
+        <is>
+          <t xml:space="preserve">TBD </t>
+        </is>
+      </c>
+      <c r="J94" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Preventive </t>
+        </is>
+      </c>
+    </row>
+    <row r="95">
+      <c r="A95" t="inlineStr">
+        <is>
+          <t xml:space="preserve">VEDA - Dearator </t>
+        </is>
+      </c>
+      <c r="B95" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Remove dissolved oxygen from process water to prevent downstream corrosion </t>
+        </is>
+      </c>
+      <c r="C95" t="inlineStr">
+        <is>
+          <t>Manhole Failure (*) *</t>
+        </is>
+      </c>
+      <c r="D95" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Provide personnel access for inspection and maintenance </t>
+        </is>
+      </c>
+      <c r="E95" t="inlineStr">
+        <is>
+          <t xml:space="preserve">NOI - Noise </t>
+        </is>
+      </c>
+      <c r="F95" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2.6 Fatigue </t>
+        </is>
+      </c>
+      <c r="G95" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Small leak through developing crack creates hissing noise </t>
+        </is>
+      </c>
+      <c r="H95" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Manhole area checked for audible leaks? [Y/N] </t>
+        </is>
+      </c>
+      <c r="I95" t="inlineStr">
+        <is>
+          <t xml:space="preserve">TBD </t>
+        </is>
+      </c>
+      <c r="J95" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Preventive </t>
+        </is>
+      </c>
+    </row>
+    <row r="96">
+      <c r="A96" t="inlineStr">
+        <is>
+          <t xml:space="preserve">VEDA - Dearator </t>
+        </is>
+      </c>
+      <c r="B96" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Remove dissolved oxygen from process water to prevent downstream corrosion </t>
+        </is>
+      </c>
+      <c r="C96" t="inlineStr">
+        <is>
+          <t>Flange/Gasket Joints Failure (*) *</t>
+        </is>
+      </c>
+      <c r="D96" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Provide leak-tight connections at all nozzle and manhole interfaces </t>
+        </is>
+      </c>
+      <c r="E96" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ELP - External leakage - process medium </t>
+        </is>
+      </c>
+      <c r="F96" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2.6 Fatigue </t>
+        </is>
+      </c>
+      <c r="G96" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Thermal cycling causes gasket relaxation and sealing loss </t>
+        </is>
+      </c>
+      <c r="H96" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Flange bolt tension verified by torque/tension values? [Y/N] </t>
+        </is>
+      </c>
+      <c r="I96" t="inlineStr">
+        <is>
+          <t xml:space="preserve">TBD </t>
+        </is>
+      </c>
+      <c r="J96" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Preventive </t>
+        </is>
+      </c>
+    </row>
+    <row r="97">
+      <c r="A97" t="inlineStr">
+        <is>
+          <t xml:space="preserve">VEDA - Dearator </t>
+        </is>
+      </c>
+      <c r="B97" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Remove dissolved oxygen from process water to prevent downstream corrosion </t>
+        </is>
+      </c>
+      <c r="C97" t="inlineStr">
+        <is>
+          <t>Flange/Gasket Joints Failure (*) *</t>
+        </is>
+      </c>
+      <c r="D97" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Provide leak-tight connections at all nozzle and manhole interfaces </t>
+        </is>
+      </c>
+      <c r="E97" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ELP - External leakage - process medium </t>
+        </is>
+      </c>
+      <c r="F97" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2.2 Corrosion </t>
+        </is>
+      </c>
+      <c r="G97" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Flange face corrosion degrades sealing surface </t>
+        </is>
+      </c>
+      <c r="H97" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Flange face condition inspected for corrosion damage? [Y/N] </t>
+        </is>
+      </c>
+      <c r="I97" t="inlineStr">
+        <is>
+          <t xml:space="preserve">TBD </t>
+        </is>
+      </c>
+      <c r="J97" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Preventive </t>
+        </is>
+      </c>
+    </row>
+    <row r="98">
+      <c r="A98" t="inlineStr">
+        <is>
+          <t xml:space="preserve">VEDA - Dearator </t>
+        </is>
+      </c>
+      <c r="B98" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Remove dissolved oxygen from process water to prevent downstream corrosion </t>
+        </is>
+      </c>
+      <c r="C98" t="inlineStr">
+        <is>
+          <t>Flange/Gasket Joints Failure (*) *</t>
+        </is>
+      </c>
+      <c r="D98" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Provide leak-tight connections at all nozzle and manhole interfaces </t>
+        </is>
+      </c>
+      <c r="E98" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ELP - External leakage - process medium </t>
+        </is>
+      </c>
+      <c r="F98" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1.4 Deformation </t>
+        </is>
+      </c>
+      <c r="G98" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gasket crushing from excessive bolt torque </t>
+        </is>
+      </c>
+      <c r="H98" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Flange gasket correctly installed and compressed? [Y/N] </t>
+        </is>
+      </c>
+      <c r="I98" t="inlineStr">
+        <is>
+          <t xml:space="preserve">TBD </t>
+        </is>
+      </c>
+      <c r="J98" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Preventive </t>
+        </is>
+      </c>
+    </row>
+    <row r="99">
+      <c r="A99" t="inlineStr">
+        <is>
+          <t xml:space="preserve">VEDA - Dearator </t>
+        </is>
+      </c>
+      <c r="B99" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Remove dissolved oxygen from process water to prevent downstream corrosion </t>
+        </is>
+      </c>
+      <c r="C99" t="inlineStr">
+        <is>
+          <t>Flange/Gasket Joints Failure (*) *</t>
+        </is>
+      </c>
+      <c r="D99" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Provide leak-tight connections at all nozzle and manhole interfaces </t>
+        </is>
+      </c>
+      <c r="E99" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ELP - External leakage - process medium </t>
+        </is>
+      </c>
+      <c r="F99" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1.3 Clearance/alignment failure </t>
+        </is>
+      </c>
+      <c r="G99" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Misaligned flanges cause uneven gasket compression </t>
+        </is>
+      </c>
+      <c r="H99" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Flange alignment before bolt-up verified? [Y/N] </t>
+        </is>
+      </c>
+      <c r="I99" t="inlineStr">
+        <is>
+          <t xml:space="preserve">TBD </t>
+        </is>
+      </c>
+      <c r="J99" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Preventive </t>
+        </is>
+      </c>
+    </row>
+    <row r="100">
+      <c r="A100" t="inlineStr">
+        <is>
+          <t xml:space="preserve">VEDA - Dearator </t>
+        </is>
+      </c>
+      <c r="B100" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Remove dissolved oxygen from process water to prevent downstream corrosion </t>
+        </is>
+      </c>
+      <c r="C100" t="inlineStr">
+        <is>
+          <t>Flange/Gasket Joints Failure (*) *</t>
+        </is>
+      </c>
+      <c r="D100" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Provide leak-tight connections at all nozzle and manhole interfaces </t>
+        </is>
+      </c>
+      <c r="E100" t="inlineStr">
+        <is>
+          <t xml:space="preserve">STD - Structural deficiency </t>
+        </is>
+      </c>
+      <c r="F100" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2.2 Corrosion </t>
+        </is>
+      </c>
+      <c r="G100" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Flange or bolt corrosion degrades mechanical strength </t>
+        </is>
+      </c>
+      <c r="H100" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Flange and bolt thickness/condition verified? [Y/N] </t>
+        </is>
+      </c>
+      <c r="I100" t="inlineStr">
+        <is>
+          <t xml:space="preserve">TBD </t>
+        </is>
+      </c>
+      <c r="J100" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Predictive </t>
+        </is>
+      </c>
+    </row>
+    <row r="101">
+      <c r="A101" t="inlineStr">
+        <is>
+          <t xml:space="preserve">VEDA - Dearator </t>
+        </is>
+      </c>
+      <c r="B101" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Remove dissolved oxygen from process water to prevent downstream corrosion </t>
+        </is>
+      </c>
+      <c r="C101" t="inlineStr">
+        <is>
+          <t>Flange/Gasket Joints Failure (*) *</t>
+        </is>
+      </c>
+      <c r="D101" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Provide leak-tight connections at all nozzle and manhole interfaces </t>
+        </is>
+      </c>
+      <c r="E101" t="inlineStr">
+        <is>
+          <t xml:space="preserve">STD - Structural deficiency </t>
+        </is>
+      </c>
+      <c r="F101" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2.6 Fatigue </t>
+        </is>
+      </c>
+      <c r="G101" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Cyclic loading causes flange bolt fatigue failure </t>
+        </is>
+      </c>
+      <c r="H101" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Flange bolts inspected for elongation/corrosion? [Y/N] </t>
+        </is>
+      </c>
+      <c r="I101" t="inlineStr">
+        <is>
+          <t xml:space="preserve">TBD </t>
+        </is>
+      </c>
+      <c r="J101" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Preventive </t>
+        </is>
+      </c>
+    </row>
+    <row r="102">
+      <c r="A102" t="inlineStr">
+        <is>
+          <t xml:space="preserve">VEDA - Dearator </t>
+        </is>
+      </c>
+      <c r="B102" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Remove dissolved oxygen from process water to prevent downstream corrosion </t>
+        </is>
+      </c>
+      <c r="C102" t="inlineStr">
+        <is>
+          <t>Flange/Gasket Joints Failure (*) *</t>
+        </is>
+      </c>
+      <c r="D102" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Provide leak-tight connections at all nozzle and manhole interfaces </t>
+        </is>
+      </c>
+      <c r="E102" t="inlineStr">
+        <is>
+          <t xml:space="preserve">PDE - Parameter deviation </t>
+        </is>
+      </c>
+      <c r="F102" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2.2 Corrosion </t>
+        </is>
+      </c>
+      <c r="G102" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Internal flange face corrosion creates leak path </t>
+        </is>
+      </c>
+      <c r="H102" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Flange face inspected during maintenance? [Y/N] </t>
+        </is>
+      </c>
+      <c r="I102" t="inlineStr">
+        <is>
+          <t xml:space="preserve">TBD </t>
+        </is>
+      </c>
+      <c r="J102" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Preventive </t>
+        </is>
+      </c>
+    </row>
+    <row r="103">
+      <c r="A103" t="inlineStr">
+        <is>
+          <t xml:space="preserve">VEDA - Dearator </t>
+        </is>
+      </c>
+      <c r="B103" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Remove dissolved oxygen from process water to prevent downstream corrosion </t>
+        </is>
+      </c>
+      <c r="C103" t="inlineStr">
+        <is>
+          <t>Flange/Gasket Joints Failure (*) *</t>
+        </is>
+      </c>
+      <c r="D103" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Provide leak-tight connections at all nozzle and manhole interfaces </t>
+        </is>
+      </c>
+      <c r="E103" t="inlineStr">
+        <is>
+          <t xml:space="preserve">PDE - Parameter deviation </t>
+        </is>
+      </c>
+      <c r="F103" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1.4 Deformation </t>
+        </is>
+      </c>
+      <c r="G103" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Flange rotation from excessive piping load </t>
+        </is>
+      </c>
+      <c r="H103" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Pipe support at flange adjusted to minimize flange stress? [Y/N] </t>
+        </is>
+      </c>
+      <c r="I103" t="inlineStr">
+        <is>
+          <t xml:space="preserve">TBD </t>
+        </is>
+      </c>
+      <c r="J103" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Preventive </t>
+        </is>
+      </c>
+    </row>
+    <row r="104">
+      <c r="A104" t="inlineStr">
+        <is>
+          <t xml:space="preserve">VEDA - Dearator </t>
+        </is>
+      </c>
+      <c r="B104" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Remove dissolved oxygen from process water to prevent downstream corrosion </t>
+        </is>
+      </c>
+      <c r="C104" t="inlineStr">
+        <is>
+          <t>Flange/Gasket Joints Failure (*) *</t>
+        </is>
+      </c>
+      <c r="D104" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Provide leak-tight connections at all nozzle and manhole interfaces </t>
+        </is>
+      </c>
+      <c r="E104" t="inlineStr">
+        <is>
+          <t xml:space="preserve">NOI - Noise </t>
+        </is>
+      </c>
+      <c r="F104" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1.5 Looseness </t>
+        </is>
+      </c>
+      <c r="G104" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Loose flange bolts cause joint movement noise under pressure </t>
+        </is>
+      </c>
+      <c r="H104" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Flange bolts verified tight? [Y/N] </t>
+        </is>
+      </c>
+      <c r="I104" t="inlineStr">
+        <is>
+          <t xml:space="preserve">TBD </t>
+        </is>
+      </c>
+      <c r="J104" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Preventive </t>
+        </is>
+      </c>
+    </row>
+    <row r="105">
+      <c r="A105" t="inlineStr">
+        <is>
+          <t xml:space="preserve">VEDA - Dearator </t>
+        </is>
+      </c>
+      <c r="B105" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Remove dissolved oxygen from process water to prevent downstream corrosion </t>
+        </is>
+      </c>
+      <c r="C105" t="inlineStr">
+        <is>
+          <t>Flange/Gasket Joints Failure (*) *</t>
+        </is>
+      </c>
+      <c r="D105" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Provide leak-tight connections at all nozzle and manhole interfaces </t>
+        </is>
+      </c>
+      <c r="E105" t="inlineStr">
+        <is>
+          <t xml:space="preserve">NOI - Noise </t>
+        </is>
+      </c>
+      <c r="F105" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1.6 Sticking </t>
+        </is>
+      </c>
+      <c r="G105" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gasket extrusion creates localized flow disturbance noise </t>
+        </is>
+      </c>
+      <c r="H105" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gasket condition verified appropriate for service? [Y/N] </t>
+        </is>
+      </c>
+      <c r="I105" t="inlineStr">
+        <is>
+          <t xml:space="preserve">TBD </t>
+        </is>
+      </c>
+      <c r="J105" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Preventive </t>
+        </is>
+      </c>
+    </row>
+    <row r="106">
+      <c r="A106" t="inlineStr">
+        <is>
+          <t xml:space="preserve">VEDA - Dearator </t>
+        </is>
+      </c>
+      <c r="B106" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Remove dissolved oxygen from process water to prevent downstream corrosion </t>
+        </is>
+      </c>
+      <c r="C106" t="inlineStr">
+        <is>
+          <t>Flange/Gasket Joints Failure (*) *</t>
+        </is>
+      </c>
+      <c r="D106" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Provide leak-tight connections at all nozzle and manhole interfaces </t>
+        </is>
+      </c>
+      <c r="E106" t="inlineStr"/>
+      <c r="F106" t="inlineStr"/>
+      <c r="G106" t="inlineStr"/>
+      <c r="H106" t="inlineStr"/>
+      <c r="I106" t="inlineStr"/>
+      <c r="J106" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
